--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -28,6 +28,11 @@
     <sheet name="Source Notes" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Action Items" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Art Generation Prompts" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Roadmap - Open Items &amp; Priority" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Roadmap - Architecture Notes" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Roadmap - Process Note" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Roadmap - Art Direction" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Implementation Waves 0-6" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,7 +96,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -151,6 +156,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FBE4D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -320,6 +330,36 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -685,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -701,7 +741,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -765,7 +804,6 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="6" t="n"/>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -1103,7 +1141,6 @@
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="6" t="n"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -1205,7 +1242,6 @@
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="6" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
@@ -1379,13 +1415,125 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="50" t="inlineStr">
+        <is>
+          <t>SHEET GUIDE ADDENDUM (2026-09-14) - added when docs/Roadmap.md and docs/IMPLEMENTATION_ROADMAP.md were retired and folded in</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="51" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>What is on it</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="39" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>From docs/Roadmap.md Sections 1 and 5 (the open-items punch list and the recommended near-term order), reconciled against actual repo state - which items are genuinely still open (Open Backlog block) vs. closed since the doc was written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="39" t="inlineStr">
+        <is>
+          <t>Roadmap - Architecture Notes</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>From docs/Roadmap.md Section 2: standing technical/design decisions worth preserving - not bugs, not tasks, permanent reference (e.g. CombatBonus and CounterMatrix are deliberately not merged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="39" t="inlineStr">
+        <is>
+          <t>Roadmap - Process Note</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>From docs/Roadmap.md Section 3: the session-discipline guidance about multi-session concurrency risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="39" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>From docs/Roadmap.md Section 4: the target visual standard table, civ-by-civ art audit findings not already on the Dev Status Overview/Action Items sheets, and the standing sourcing/creation checklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="39" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>From docs/IMPLEMENTATION_ROADMAP.md in full: all 40 scoped, dependency-ordered items plus the asset-blocked track, each with size/dependencies/current status. OPEN THIS to find the next scoped, session-sized task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="50" t="inlineStr">
+        <is>
+          <t>SOURCE DOCS RETIRED 2026-09-14 (addendum to the source-workbooks list above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>docs/Roadmap.md (REMOVED 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>'Master Roadmap v3' - Sections 1-5 (open items, architectural notes, process note, art direction, priority order) plus a Section 6 status summary of docs/AOE_PARITY_EXECUTION_PLAN.md. Content fully preserved on the 4 new 'Roadmap - *' sheets above; Section 6's AoE-Parity phase detail was condensed rather than re-duplicated, since the Dev Status Overview sheet already carries an equivalent, more current Phase 1-5 summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>docs/IMPLEMENTATION_ROADMAP.md (REMOVED 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>The dependency-ordered Wave 0-6 execution plan, 40 items. Content fully preserved on the 'Implementation Waves 0-6' sheet above, including the asset-blocked track and the summary table.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="55">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="B13:D13"/>
@@ -1399,13 +1547,18 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A70:D70"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
@@ -1416,9 +1569,12 @@
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B71:D71"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
@@ -15137,7 +15293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E439"/>
+  <dimension ref="A1:E530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -26930,6 +27086,2463 @@
       <c r="E439" s="44" t="inlineStr">
         <is>
           <t>Action Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B440" s="22" t="inlineStr">
+        <is>
+          <t>Training UI gaps (Cavalry/Siege/Dock/Spearman train buttons)</t>
+        </is>
+      </c>
+      <c r="C440" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D440" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E440" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B441" s="22" t="inlineStr">
+        <is>
+          <t>Market trade UI (Buy/Sell buttons on BuildMenu)</t>
+        </is>
+      </c>
+      <c r="C441" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D441" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E441" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B442" s="22" t="inlineStr">
+        <is>
+          <t>Multiplayer determinism gaps</t>
+        </is>
+      </c>
+      <c r="C442" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="D442" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E442" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B443" s="22" t="inlineStr">
+        <is>
+          <t>WaterMover has no obstacle avoidance</t>
+        </is>
+      </c>
+      <c r="C443" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D443" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E443" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B444" s="22" t="inlineStr">
+        <is>
+          <t>Wall's NavMeshObstacle carving never confirmed live</t>
+        </is>
+      </c>
+      <c r="C444" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D444" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E444" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B445" s="22" t="inlineStr">
+        <is>
+          <t>AoE-style building footprint rules</t>
+        </is>
+      </c>
+      <c r="C445" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D445" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E445" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B446" s="22" t="inlineStr">
+        <is>
+          <t>Building mesh decimation pass</t>
+        </is>
+      </c>
+      <c r="C446" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D446" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E446" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B447" s="22" t="inlineStr">
+        <is>
+          <t>Worker mechanics audit vs. AoE reference behavior</t>
+        </is>
+      </c>
+      <c r="C447" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D447" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E447" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B448" s="22" t="inlineStr">
+        <is>
+          <t>Dedicated resource-specific drop-off buildings</t>
+        </is>
+      </c>
+      <c r="C448" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D448" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E448" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B449" s="22" t="inlineStr">
+        <is>
+          <t>Team-bonus / alliance economic stacking layer</t>
+        </is>
+      </c>
+      <c r="C449" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D449" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E449" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B450" s="22" t="inlineStr">
+        <is>
+          <t>Worker self-defense/cross-awareness</t>
+        </is>
+      </c>
+      <c r="C450" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D450" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E450" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B451" s="22" t="inlineStr">
+        <is>
+          <t>Repair system</t>
+        </is>
+      </c>
+      <c r="C451" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D451" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E451" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B452" s="22" t="inlineStr">
+        <is>
+          <t>General garrisoning system, AoE IV style</t>
+        </is>
+      </c>
+      <c r="C452" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D452" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E452" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B453" s="22" t="inlineStr">
+        <is>
+          <t>4 unique units for Maurya/Maratha have no live factory</t>
+        </is>
+      </c>
+      <c r="C453" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D453" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E453" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B454" s="22" t="inlineStr">
+        <is>
+          <t>Narrower per-civ passive bonuses aren't live</t>
+        </is>
+      </c>
+      <c r="C454" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D454" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E454" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B455" s="22" t="inlineStr">
+        <is>
+          <t>Balance pass (item 43) resumed</t>
+        </is>
+      </c>
+      <c r="C455" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D455" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E455" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B456" s="22" t="inlineStr">
+        <is>
+          <t>Naval balance is one evidenced fix, not a full pass</t>
+        </is>
+      </c>
+      <c r="C456" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D456" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E456" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B457" s="22" t="inlineStr">
+        <is>
+          <t>UI skin (item 47's second half)</t>
+        </is>
+      </c>
+      <c r="C457" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D457" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E457" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B458" s="22" t="inlineStr">
+        <is>
+          <t>2 Crusader Knight body models sourced but not wired in</t>
+        </is>
+      </c>
+      <c r="C458" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D458" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E458" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B459" s="22" t="inlineStr">
+        <is>
+          <t>Per-civ soldier visual differentiation</t>
+        </is>
+      </c>
+      <c r="C459" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="D459" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E459" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B460" s="22" t="inlineStr">
+        <is>
+          <t>AoE-parity Phase 2 - Combat calibration audit</t>
+        </is>
+      </c>
+      <c r="C460" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D460" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E460" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B461" s="22" t="inlineStr">
+        <is>
+          <t>Music is entirely absent</t>
+        </is>
+      </c>
+      <c r="C461" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D461" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E461" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B462" s="22" t="inlineStr">
+        <is>
+          <t>No dedicated new-player tutorial</t>
+        </is>
+      </c>
+      <c r="C462" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D462" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E462" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B463" s="22" t="inlineStr">
+        <is>
+          <t>No profiling/optimization pass at real scale</t>
+        </is>
+      </c>
+      <c r="C463" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D463" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E463" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B464" s="22" t="inlineStr">
+        <is>
+          <t>Store/marketing assets</t>
+        </is>
+      </c>
+      <c r="C464" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D464" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E464" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B465" s="22" t="inlineStr">
+        <is>
+          <t>README drift (repo root README.md, not this workbook)</t>
+        </is>
+      </c>
+      <c r="C465" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D465" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E465" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B466" s="22" t="inlineStr">
+        <is>
+          <t>Fish Trap (water-adjacent Food building)</t>
+        </is>
+      </c>
+      <c r="C466" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D466" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E466" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B467" s="22" t="inlineStr">
+        <is>
+          <t>Multiplayer: cross-machine determinism testing</t>
+        </is>
+      </c>
+      <c r="C467" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D467" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E467" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B468" s="22" t="inlineStr">
+        <is>
+          <t>Crusader Knight body-swap (replace shared Human Character Dummy)</t>
+        </is>
+      </c>
+      <c r="C468" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D468" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E468" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B469" s="22" t="inlineStr">
+        <is>
+          <t>Per-civ unit gear (helmet/shield/weapon variants)</t>
+        </is>
+      </c>
+      <c r="C469" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D469" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E469" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B470" s="22" t="inlineStr">
+        <is>
+          <t>Music (soundtrack)</t>
+        </is>
+      </c>
+      <c r="C470" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D470" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E470" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B471" s="22" t="inlineStr">
+        <is>
+          <t>Tutorial content</t>
+        </is>
+      </c>
+      <c r="C471" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D471" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E471" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B472" s="22" t="inlineStr">
+        <is>
+          <t>Performance/optimization profiling pass</t>
+        </is>
+      </c>
+      <c r="C472" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D472" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E472" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B473" s="22" t="inlineStr">
+        <is>
+          <t>Store/marketing assets</t>
+        </is>
+      </c>
+      <c r="C473" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D473" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E473" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B474" s="22" t="inlineStr">
+        <is>
+          <t>README.md drift (repo root)</t>
+        </is>
+      </c>
+      <c r="C474" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D474" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E474" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B475" s="22" t="inlineStr">
+        <is>
+          <t>Fish Trap building</t>
+        </is>
+      </c>
+      <c r="C475" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D475" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E475" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+      <c r="B476" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6 backlog items 34-40 (idle-worker indicator, Relics, Score, Wonder/Relic victory conditions, game modes, cheat codes, tutorial, soundtrack)</t>
+        </is>
+      </c>
+      <c r="C476" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="D476" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E476" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B477" s="22" t="inlineStr">
+        <is>
+          <t>Sample unique unit (Pillar Edict Scholar, Maurya) passes cleanly</t>
+        </is>
+      </c>
+      <c r="C477" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D477" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E477" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B478" s="22" t="inlineStr">
+        <is>
+          <t>War Galley (shared naval unit) mixes two shaders on one model</t>
+        </is>
+      </c>
+      <c r="C478" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D478" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E478" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B479" s="22" t="inlineStr">
+        <is>
+          <t>Environment props (trees, mines, quarries, farmland) not poly/texture-audited</t>
+        </is>
+      </c>
+      <c r="C479" s="57" t="inlineStr">
+        <is>
+          <t>[?] Unclear / needs verification</t>
+        </is>
+      </c>
+      <c r="D479" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E479" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B480" s="22" t="inlineStr">
+        <is>
+          <t>Maurya's TownCenter reads architecturally closer to Mughal/colonial than actual Mauryan-era style</t>
+        </is>
+      </c>
+      <c r="C480" s="57" t="inlineStr">
+        <is>
+          <t>[?] Unclear / needs verification</t>
+        </is>
+      </c>
+      <c r="D480" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E480" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B481" s="22" t="inlineStr">
+        <is>
+          <t>Chola and Vijayanagara TownCenters read as the same architectural family at a glance</t>
+        </is>
+      </c>
+      <c r="C481" s="57" t="inlineStr">
+        <is>
+          <t>[?] Unclear / needs verification</t>
+        </is>
+      </c>
+      <c r="D481" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E481" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B482" s="22" t="inlineStr">
+        <is>
+          <t>Per-civ architectural differentiation - overall visual-fidelity gap</t>
+        </is>
+      </c>
+      <c r="C482" s="58" t="inlineStr">
+        <is>
+          <t>[R] Superseded</t>
+        </is>
+      </c>
+      <c r="D482" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E482" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+      <c r="B483" s="22" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="C483" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D483" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E483" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Art Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B484" s="22" t="inlineStr">
+        <is>
+          <t>Item 1 - Reconcile UnitClass vs UnitCategory</t>
+        </is>
+      </c>
+      <c r="C484" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D484" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E484" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B485" s="22" t="inlineStr">
+        <is>
+          <t>Item 2 - Verify the retroactive upgrade rule</t>
+        </is>
+      </c>
+      <c r="C485" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D485" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E485" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B486" s="22" t="inlineStr">
+        <is>
+          <t>Item 3 - Confirm the minimum-damage clamp</t>
+        </is>
+      </c>
+      <c r="C486" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D486" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E486" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B487" s="22" t="inlineStr">
+        <is>
+          <t>Item 4 - Wire DamageType.Trample and DamageType.Fire</t>
+        </is>
+      </c>
+      <c r="C487" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D487" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E487" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B488" s="22" t="inlineStr">
+        <is>
+          <t>Item 5 - Add AgeId.Durg</t>
+        </is>
+      </c>
+      <c r="C488" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D488" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E488" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B489" s="22" t="inlineStr">
+        <is>
+          <t>Item 6 - Age-up building-count requirement</t>
+        </is>
+      </c>
+      <c r="C489" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D489" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E489" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B490" s="22" t="inlineStr">
+        <is>
+          <t>Item 7 - Durg building</t>
+        </is>
+      </c>
+      <c r="C490" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D490" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E490" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B491" s="22" t="inlineStr">
+        <is>
+          <t>Item 8 - Karmashala (Blacksmith-equivalent building)</t>
+        </is>
+      </c>
+      <c r="C491" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D491" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E491" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B492" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 - Infantry line (5 tiers)</t>
+        </is>
+      </c>
+      <c r="C492" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D492" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E492" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B493" s="22" t="inlineStr">
+        <is>
+          <t>Item 10 - Spearman line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="C493" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D493" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E493" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B494" s="22" t="inlineStr">
+        <is>
+          <t>Item 11 - Archer line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="C494" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D494" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E494" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B495" s="22" t="inlineStr">
+        <is>
+          <t>Item 12 - Knight/Cavalry line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="C495" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D495" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E495" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B496" s="22" t="inlineStr">
+        <is>
+          <t>Item 13 - Elephant line (2 tiers, KoB's own invention)</t>
+        </is>
+      </c>
+      <c r="C496" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D496" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E496" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B497" s="22" t="inlineStr">
+        <is>
+          <t>Item 14 - Mangonel/Siege line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="C497" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D497" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E497" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B498" s="22" t="inlineStr">
+        <is>
+          <t>Item 15 - Galley/Naval line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="C498" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D498" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E498" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B499" s="22" t="inlineStr">
+        <is>
+          <t>Item 16 - Unique-unit Elite tier (2 tiers x 5 units, was 7 - see item 13)</t>
+        </is>
+      </c>
+      <c r="C499" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D499" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E499" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B500" s="22" t="inlineStr">
+        <is>
+          <t>Item 17 - Blacksmith-style stat upgrade steps (age-gate Karmashala's 3 tiers)</t>
+        </is>
+      </c>
+      <c r="C500" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D500" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E500" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B501" s="22" t="inlineStr">
+        <is>
+          <t>Item 18 - Scout (Chara), 3-tier line</t>
+        </is>
+      </c>
+      <c r="C501" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D501" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E501" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B502" s="22" t="inlineStr">
+        <is>
+          <t>Item 19 - Skirmisher (anti-archer counter-archer), 2 tiers</t>
+        </is>
+      </c>
+      <c r="C502" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D502" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E502" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B503" s="22" t="inlineStr">
+        <is>
+          <t>Item 20 - Battering Ram, 3 tiers</t>
+        </is>
+      </c>
+      <c r="C503" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D503" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E503" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B504" s="22" t="inlineStr">
+        <is>
+          <t>Item 21 - Cavalry Archer, 2 tiers</t>
+        </is>
+      </c>
+      <c r="C504" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D504" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E504" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B505" s="22" t="inlineStr">
+        <is>
+          <t>Item 22 - Camel Rider, 2 tiers (design decision first)</t>
+        </is>
+      </c>
+      <c r="C505" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D505" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E505" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B506" s="22" t="inlineStr">
+        <is>
+          <t>Item 23 - Scorpion, 2 tiers</t>
+        </is>
+      </c>
+      <c r="C506" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D506" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E506" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B507" s="22" t="inlineStr">
+        <is>
+          <t>Item 24 - Trebuchet, 1 tier</t>
+        </is>
+      </c>
+      <c r="C507" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D507" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E507" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B508" s="22" t="inlineStr">
+        <is>
+          <t>Item 25 - Fire Ship, 3 tiers</t>
+        </is>
+      </c>
+      <c r="C508" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D508" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E508" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B509" s="22" t="inlineStr">
+        <is>
+          <t>Item 26 - Trader (land + naval), design decision first</t>
+        </is>
+      </c>
+      <c r="C509" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D509" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E509" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B510" s="22" t="inlineStr">
+        <is>
+          <t>Item 27 - Support units - Vaidya (healer) and Purohita (converter)</t>
+        </is>
+      </c>
+      <c r="C510" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D510" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E510" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B511" s="22" t="inlineStr">
+        <is>
+          <t>Item 28 - Hero unit - Maharaja, per civ</t>
+        </is>
+      </c>
+      <c r="C511" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D511" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E511" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B512" s="22" t="inlineStr">
+        <is>
+          <t>Item 29 - Player/team colour system</t>
+        </is>
+      </c>
+      <c r="C512" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="D512" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E512" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B513" s="22" t="inlineStr">
+        <is>
+          <t>Item 30 - UI layout re-anchor - bottom bar</t>
+        </is>
+      </c>
+      <c r="C513" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D513" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E513" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B514" s="22" t="inlineStr">
+        <is>
+          <t>Item 31 - BuildMenu command-panel grid redesign</t>
+        </is>
+      </c>
+      <c r="C514" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D514" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E514" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B515" s="22" t="inlineStr">
+        <is>
+          <t>Item 32 - Age/research always-visible readout</t>
+        </is>
+      </c>
+      <c r="C515" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D515" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E515" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B516" s="22" t="inlineStr">
+        <is>
+          <t>Item 33 - Town Bell</t>
+        </is>
+      </c>
+      <c r="C516" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D516" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E516" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B517" s="22" t="inlineStr">
+        <is>
+          <t>Item 34 - Idle-worker indicator</t>
+        </is>
+      </c>
+      <c r="C517" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D517" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E517" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B518" s="22" t="inlineStr">
+        <is>
+          <t>Item 35 - Relics + Monastery-equivalent, if wanted</t>
+        </is>
+      </c>
+      <c r="C518" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D518" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E518" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B519" s="22" t="inlineStr">
+        <is>
+          <t>Item 36 - Score system</t>
+        </is>
+      </c>
+      <c r="C519" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D519" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E519" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B520" s="22" t="inlineStr">
+        <is>
+          <t>Item 37 - Victory conditions beyond Conquest</t>
+        </is>
+      </c>
+      <c r="C520" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="D520" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E520" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B521" s="22" t="inlineStr">
+        <is>
+          <t>Item 38 - Game modes</t>
+        </is>
+      </c>
+      <c r="C521" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D521" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E521" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B522" s="22" t="inlineStr">
+        <is>
+          <t>Item 39 - Cheat codes</t>
+        </is>
+      </c>
+      <c r="C522" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D522" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E522" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B523" s="22" t="inlineStr">
+        <is>
+          <t>Item 40 - Tutorial content</t>
+        </is>
+      </c>
+      <c r="C523" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D523" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E523" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B524" s="22" t="inlineStr">
+        <is>
+          <t>Item 40b - Soundtrack</t>
+        </is>
+      </c>
+      <c r="C524" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D524" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E524" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B525" s="22" t="inlineStr">
+        <is>
+          <t>Villager (Praja) art</t>
+        </is>
+      </c>
+      <c r="C525" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D525" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E525" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B526" s="22" t="inlineStr">
+        <is>
+          <t>Town Center age-variants (4 ages x 5 civs)</t>
+        </is>
+      </c>
+      <c r="C526" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="D526" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E526" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B527" s="22" t="inlineStr">
+        <is>
+          <t>Tower and Wall upgrade tiers</t>
+        </is>
+      </c>
+      <c r="C527" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="D527" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E527" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B528" s="22" t="inlineStr">
+        <is>
+          <t>Drop-off building art (Lumber Camp / Mining Camp / Mill)</t>
+        </is>
+      </c>
+      <c r="C528" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D528" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E528" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B529" s="22" t="inlineStr">
+        <is>
+          <t>Per-civ unit gear (helmet/shield/weapon variants)</t>
+        </is>
+      </c>
+      <c r="C529" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="D529" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E529" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+      <c r="B530" s="22" t="inlineStr">
+        <is>
+          <t>New-unit models for every Wave 4 item</t>
+        </is>
+      </c>
+      <c r="C530" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="D530" s="22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION_ROADMAP.md (retired, folded in 2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E530" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
         </is>
       </c>
     </row>
@@ -28094,7 +30707,7 @@
         </is>
       </c>
       <c r="B27" s="20">
-        <f>COUNTIF('Status Index'!$C$5:$C$439,A27)</f>
+        <f>COUNTIF('Status Index'!$C$5:$C$530,A27)</f>
         <v/>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -28110,7 +30723,7 @@
         </is>
       </c>
       <c r="B28" s="20">
-        <f>COUNTIF('Status Index'!$C$5:$C$439,A28)</f>
+        <f>COUNTIF('Status Index'!$C$5:$C$530,A28)</f>
         <v/>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -28126,7 +30739,7 @@
         </is>
       </c>
       <c r="B29" s="20">
-        <f>COUNTIF('Status Index'!$C$5:$C$439,A29)</f>
+        <f>COUNTIF('Status Index'!$C$5:$C$530,A29)</f>
         <v/>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -28142,7 +30755,7 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>COUNTIF('Status Index'!$C$5:$C$439,A30)</f>
+        <f>COUNTIF('Status Index'!$C$5:$C$530,A30)</f>
         <v/>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -28158,7 +30771,7 @@
         </is>
       </c>
       <c r="B31" s="20">
-        <f>COUNTIF('Status Index'!$C$5:$C$439,A31)</f>
+        <f>COUNTIF('Status Index'!$C$5:$C$530,A31)</f>
         <v/>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -28174,7 +30787,7 @@
         </is>
       </c>
       <c r="B32" s="20">
-        <f>COUNTIF('Status Index'!$C$5:$C$439,A32)</f>
+        <f>COUNTIF('Status Index'!$C$5:$C$530,A32)</f>
         <v/>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -28253,7 +30866,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>- UI: ornate HUD art pass (UI_ART_BRIEF Tiers 1-3), AoE-style single bottom bar, paginated icon command grid with tooltips, group-selection icon row, and an always-visible Age/research meter.</t>
+          <t>- UI: ornate HUD art pass (UI_ART_BRIEF Tiers 1-3), AoE-style single bottom bar, paginated icon command grid with tooltips, group-selection icon row, an always-visible Age/research meter, and (2026-09-14) SelectedUnitPanel portrait display wiring for the 21 generic-unit portraits, including TradeShipFactory's IconKey.</t>
         </is>
       </c>
     </row>
@@ -28267,23 +30880,19 @@
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>- Unit portrait wiring - 21 generic-unit portraits were alpha-keyed, circle-cropped and committed on 2026-09-14, but the SelectedUnitPanel display code was NOT wired (Unity/UnityMCP was unreachable that session and the user chose to hold rather than guess measurements). TradeShipFactory also still stamps no Unit.IconKey.</t>
+          <t>- Team colour on UNITS - Core/TeamColorUnitTint.cs exists as an uncommitted pilot in the working tree; the unit-side accent masks it needs must be painted in Blender (docs/TEAM_COLOR_ART_BRIEF.md), because the unit textures are UV atlases with no 2D spatial coherence.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Team colour on UNITS - Core/TeamColorUnitTint.cs exists as an uncommitted pilot in the working tree; the unit-side accent masks it needs must be painted in Blender (docs/TEAM_COLOR_ART_BRIEF.md), because the unit textures are UV atlases with no 2D spatial coherence.</t>
+          <t>- Wave 6 backlog - 8 of 9 items still open, all parallel-safe. The three needing no design decision are the idle-worker indicator, cheat codes and tutorial content.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>- Wave 6 backlog - 8 of 9 items still open, all parallel-safe. The three needing no design decision are the idle-worker indicator, cheat codes and tutorial content.</t>
-        </is>
-      </c>
+      <c r="A48" s="22" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -28489,30 +31098,26 @@
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>- UniqueTechDefinition.Bonuses covers only Chola, Vijayanagara and Rajput - selecting a Maurya or Maratha Barracks throws KeyNotFoundException every frame (flagged 2026-09-04 as task_55dbb0cc, still open).</t>
+          <t>- Two pre-existing BuildingModelFactoryTests failures (Chola TownCenter model) are the stable baseline in every recent session - 520 of 522 EditMode tests pass.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>- Two pre-existing BuildingModelFactoryTests failures (Chola TownCenter model) are the stable baseline in every recent session - 520 of 522 EditMode tests pass.</t>
+          <t>- A second, concurrent session was observed committing to this same branch on 2026-09-14. Re-check git status before every commit.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>- A second, concurrent session was observed committing to this same branch on 2026-09-14. Re-check git status before every commit.</t>
+          <t>- Recurring environment traps worth knowing: Unity's MCP console bridge can report zero errors while code genuinely fails to compile (check ~/Library/Logs/Unity/Editor.log directly), and exiting Play mode does not itself trigger a domain reload, so static state can bleed into the next EditMode run.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="22" t="inlineStr">
-        <is>
-          <t>- Recurring environment traps worth knowing: Unity's MCP console bridge can report zero errors while code genuinely fails to compile (check ~/Library/Logs/Unity/Editor.log directly), and exiting Play mode does not itself trigger a domain reload, so static state can bleed into the next EditMode run.</t>
-        </is>
-      </c>
+      <c r="A67" s="22" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -28524,7 +31129,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. The natural candidates now: (1) finish the SelectedUnitPanel portrait wiring plus TradeShipFactory's missing IconKey, the only work explicitly left mid-flight; (2) pick up Wave 6's decision-free items - idle-worker indicator, cheat codes, tutorial content; (3) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (4) fix the open Maurya/Maratha UniqueTechDefinition crash; (5) refresh the confirmed-stale README.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. Two items this sheet previously listed as open turned out already closed once checked directly against the repo on 2026-09-14 (portrait display wiring - commit 42a5a2c; the Maurya/Maratha UniqueTechDefinition crash - commit 6c3d21c, with regression tests) - a reminder to verify status against Assets/Scripts before starting, not just this sheet. The natural remaining candidates: (1) pick up Wave 6's decision-free items - idle-worker indicator, cheat codes, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) refresh the confirmed-stale README; (4) unit-side team colour once Blender masks are sourced.</t>
         </is>
       </c>
     </row>
@@ -30555,6 +33160,3871 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>ROADMAP - OPEN ITEMS &amp; PRIORITY (from docs/Roadmap.md Sections 1 and 5, retired 2026-09-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md's own Section 1 punch list and Section 5 priority order, reconciled against the actual repo state as of 2026-09-14 (cross-checked against the Dev Status Overview and Status Index sheets, and CLAUDE.md's session log). Nearly everything on the original punch list has since closed; what's still genuinely open is called out in the OPEN BACKLOG block at the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>SECTION 1 - GENUINELY OPEN ITEMS (the punch list as originally written)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>Priority Tier (as written)</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>Dev Status (2026-09-14)</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>Source Workbook</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>Source Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Training UI gaps (Cavalry/Siege/Dock/Spearman train buttons)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>BuildMenu.cs got Barracks Cavalry/Siege/Spearman buttons and a new Dock panel, following the existing Soldier/Archer CommandBus/TrainCommand pattern.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Market trade UI (Buy/Sell buttons on BuildMenu)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>New Market panel in BuildMenu.cs with Sell/Buy buttons for Wood/Food/Stone at a fixed 50-unit increment.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Multiplayer determinism gaps</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D8" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>BuildingPlacer now routes through CommandBus (closed); resync-on-desync via StateHash closed; real LAN transport MVP closed and live-verified over real TCP sockets (2026-09-02). STILL OPEN: true cross-machine NavMeshAgent/physics determinism testing needs a second physical machine. Online play/matchmaking/NAT traversal deferred to 'end of project' by explicit user instruction.</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>WaterMover has no obstacle avoidance</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>WaterMover.MoveTo now clamps destinations into the water region (WaterProximity.ClampToWater) so boats can't sail onto land. Real non-convex-coastline pathfinding stays out of scope (no map defines one).</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Wall's NavMeshObstacle carving never confirmed live</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Live-confirmed in a naturally-ticking Play mode session; a completed Wall carves the NavMesh and units detour around it. Fixed as a side effect of the building-footprint item's ConstructionSite squash-to-visual-child change.</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>AoE-style building footprint rules</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>New BuildingFootprint.cs: per-tile AABB placement/overlap checks and NavMeshObstacle carving (with a 0.5-unit margin) for every building type, not just Wall/Gate/Tower.</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Building mesh decimation pass</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>UnityMeshSimplifier + BuildingMeshDecimator.cs; 43/45 civ-specific buildings (2 pre-existing gaps correctly skipped, since re-sourced) decimated from ~1.7-2.0M tris down to ~500,000 each - the literal 8,000-20,000 spec target proved unreachable without visible artifacts or impractical simplifier settings. New BuildingPolycountTests.cs regression coverage.</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Worker mechanics audit vs. AoE reference behavior</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D13" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Audited Gatherer/Farm/LivestockWorker/Builder/combat. Multi-builder construction fixed to AoE II's diminishing-returns curve same session; repair, general garrisoning, resource-specific drop-offs, and self-defense/cross-awareness each closed as their own items (see rows below).</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Dedicated resource-specific drop-off buildings</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>New Lumber Camp (Wood) / Mining Camp (Gold+Stone) / Mill (Food), each a valid Gatherer drop-off only for its own resource type via Gatherer.AcceptsDropOff; TownCenter stays the universal drop-off. Art is still procedural silhouettes (see Art Direction sheet).</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>Team-bonus / alliance economic stacking layer</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D15" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>New TeamBonus.cs shares a diluted version of each civ's own unique-tech identity with every DiplomacyRegistry-allied faction (Maurya -25% Wood on Houses, Vijayanagara +15% fortification HP, Rajput +1 flat Cavalry damage, Maratha +10% Cavalry speed, Chola narrower Market spread).</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Worker self-defense/cross-awareness</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>New Attackable.OnDamaged event, CombatResponse (Fight/Flee), WorkerCombatResponseDefaults per civ - every civ's Workers fight back when attacked mid-gather except Maratha's, which flee (guerrilla identity).</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>Repair system</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>New Repairable (target-side) / Repairer (worker-side) mirror ConstructionSite/Builder's shape, reusing its diminishing-returns multi-worker formula. Wired onto all 9 building kinds, Siege, and both naval units.</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>General garrisoning system, AoE IV style</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Garrison generalized into GarrisonPoint (pooled capacity), DurgGarrisonWorker into GarrisonSeeker, TowerAttacker into BuildingAttacker so TownCenter got its first-ever Attacker. Wall keeps its old durgOnly single-slot behavior on the same class; Siege units excluded from garrisoning.</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>4 unique units for Maurya/Maratha have no live factory</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D19" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>Real Meshy-sourced models rigged (3 onto the shared human rig, the War Elephant onto a real elephant skeleton) and wired into all 4 factories.</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Narrower per-civ passive bonuses aren't live</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D20" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr"/>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Balance pass (item 43) resumed</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>[OK] Implemented (scoped)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>playtest_log.csv has 15 real fights logged; roster coverage gaps filled; civ/age/upgrade stacking audited (no code fix needed). Training cost-vs-power ratios and continued sustained playtesting remain open-ended future work, not a closed backlog item.</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>Naval balance is one evidenced fix, not a full pass</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D22" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>4 live forced-fights; no CombatBonus changes needed. 2 adjacent findings (WarGalleyFactory not applying UpgradeProgress class bonuses; BoatAttacker's 1.5s vs MeleeAttacker's 1.0s interval) both closed 2026-09-02.</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>UI skin (item 47's second half)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D23" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>Tiers 1-3 art delivered, alpha-fixed, and wired (see Action Items / Art Generation Prompts sheets for the full asset-by-asset breakdown). Tier 4 (portraits) is partial - see the Open Backlog block below.</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>2 Crusader Knight body models sourced but not wired in</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Rig-compatibility was verified positive (2026-08-28), but the 2 source glTF files (Assets/importedmodels/Item47/TemplarKnight, HospitalierKnight) were deleted the same day as 'confirmed-unused asset scrap' and are not recoverable from git history in usable form. Blocked on re-sourcing; user chose to stop rather than restore when told. See the Crusader Knight body-swap row in the Open Backlog block.</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>Per-civ soldier visual differentiation</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>Session 1 (2026-09-01) fixed the real Maurya/Maratha untinted-white tint bug (all 5 civs now tint correctly) and made the base-body decision explicitly: keep the current Human Character Dummy, don't swap to Crusader Knight this round. Body swap and gear/prop variants remain open - see Open Backlog block and Art Direction sheet.</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>AoE-parity Phase 2 - Combat calibration audit</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Archer-vs-Cavalry raised 1.5x to 2.0x after a numeric audit (old value was a near coin-flip). Infantry-vs-Archer/Cavalry-vs-Infantry audited and left unchanged (already decisive). See Dev Status Overview sheet's AoE-Parity Execution Plan section for full Phase 1-5 status.</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>Music is entirely absent</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-03: self-serve CC0 tracks from Kenney.nl, same sourcing approach as the existing Audio/SfxPlayer.cs SFX pass. Zero blocker, cheapest of the 'everything else' items.</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>No dedicated new-player tutorial</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-03: rides the existing MissionObjective/MissionTrigger system, pure content authoring, no new system needed. Zero blocker.</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>No profiling/optimization pass at real scale</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-03: mcp__UnityMCP__manage_profiler is a ready tool; needs someone to actually run it against a realistic large-match scenario. Zero blocker, no known urgent problem driving it.</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>Store/marketing assets</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D30" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Genuinely blocked on a user decision, not sourcing/code: needs an explicit ruling on whether public release is even a goal before any scoping can proceed.</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>README drift (repo root README.md, not this workbook)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>The root README.md still describes the original single-map/3-civ/no-naval prototype scope and stops its milestone list at 26 - confirmed badly stale 2026-09-03. Pure doc-writing, zero blocker.</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>Fish Trap (water-adjacent Food building)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Genuinely new content, not a fix - no FishTrap script/model/factory exists anywhere. Blocked on the user sourcing a model (1 generic, or 1 per civ). Once a model exists, wiring is small mechanical work mirroring Farm/FarmFactory's depletion+reseed shape.</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="50" t="inlineStr">
+        <is>
+          <t>SECTION 5 - RECOMMENDED NEAR-TERM ORDER (Roadmap.md's own sequencing, historical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>This was Roadmap.md's session-by-session execution order. It is almost entirely superseded by completion (cross-references items above and on the Art Direction sheet); kept here for historical sequencing context, not as a live backlog. Items 1-9, 11-17 are all Done. Item 10 is the still-open per-civ soldier differentiation gap (see above). Item 6 ('everything else') is the Music/Tutorial/Profiling/Store-assets/README backlog captured above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="inlineStr">
+        <is>
+          <t>OPEN BACKLOG - what is genuinely still 'what's next' as of 2026-09-14 (cross-checked against Dev Status Overview)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B38" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>Blocked on</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>Dev Status</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F38" s="51" t="inlineStr">
+        <is>
+          <t>Source Workbook</t>
+        </is>
+      </c>
+      <c r="G38" s="51" t="inlineStr">
+        <is>
+          <t>Source Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>Multiplayer: cross-machine determinism testing</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>A second physical machine</t>
+        </is>
+      </c>
+      <c r="D39" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>Everything else in Phase 5 is done and live-verified over real TCP sockets within one machine; this specific test needs two separate physical machines.</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>Crusader Knight body-swap (replace shared Human Character Dummy)</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Art re-sourcing (source glTFs deleted)</t>
+        </is>
+      </c>
+      <c r="D40" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>Rig compatibility proven positive once; needs the 2 source files restored or replacements sourced before the ~247x humanScale fix / weapon re-parenting work can resume.</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Per-civ unit gear (helmet/shield/weapon variants)</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Art sourcing</t>
+        </is>
+      </c>
+      <c r="D41" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>WeaponAttachment's hand-bone plumbing already exists; only the art is missing. The largest single unit-art gap per Dev Status Overview.</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Music (soundtrack)</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Self-serve CC0 tracks from Kenney.nl, same approach as the existing SFX pass.</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>Tutorial content</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker</t>
+        </is>
+      </c>
+      <c r="D43" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>Rides the existing MissionObjective/MissionTrigger system.</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>Performance/optimization profiling pass</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker</t>
+        </is>
+      </c>
+      <c r="D44" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>mcp__UnityMCP__manage_profiler is ready; just needs to be run at real match scale.</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>Store/marketing assets</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>A user decision (public release goal?)</t>
+        </is>
+      </c>
+      <c r="D45" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr"/>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t>README.md drift (repo root)</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed stale 2026-09-03; stops its own milestone list at item 26.</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>Fish Trap building</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>Art sourcing (a model)</t>
+        </is>
+      </c>
+      <c r="D47" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>AoE's naval-economy counterpart to Farm; no script/model/factory exists yet.</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>Wave 6 backlog items 34-40 (idle-worker indicator, Relics, Score, Wonder/Relic victory conditions, game modes, cheat codes, tutorial, soundtrack)</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Mostly nothing; Relics/Wonder/game modes need a design decision</t>
+        </is>
+      </c>
+      <c r="D48" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>See the Implementation Waves 0-6 sheet for the full per-item breakdown. Item 33 (Town Bell) is the only Wave 6 item closed so far (2026-09-14).</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap.md (retired)</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>ROADMAP - ARCHITECTURE NOTES (from docs/Roadmap.md Section 2, retired 2026-09-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Standing technical/design decisions worth preserving - NOT bugs, and NOT tasks. Easy for a future session to 'fix' by mistake if not written down. No status column: these are permanent reference, not status-bearing backlog items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>CombatBonus and CounterMatrix are deliberately NOT merged</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>CombatBonus holds the playtested, balance-verified UnitClass pairings (including the asymmetric Cavalry-vs-Archer fix); CounterMatrix is real CSV-generated data used only for Spearman, the one genuinely new unit category it introduced. Don't 'clean this up' into one system without re-verifying every existing balance fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>AgeProfile/UpgradeProgress are intentionally still hardcoded</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Not migrated to the CSV pipeline - they're pure formula tuning (tiers/multipliers) with no natural per-row CSV shape, not an oversight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>UniqueTechDefinition's bespoke per-civ effect values stay hardcoded</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>The CSV only carries flavor-text descriptions for unique techs, not structured effect data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>The project has real .asmdef assemblies now</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>KingdomsOfBharat.Runtime/.Editor/.Tests, added when the training/trade UI batch needed its first tests - see CLAUDE.md's gotchas section for the full layout. Don't 'flatten' this back to the implicit default assembly - it's what makes Assets/Tests possible at all.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="130" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>ROADMAP - PROCESS NOTE (from docs/Roadmap.md Section 3, retired 2026-09-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Worth reading before the next session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>The source log shows several real bugs caused specifically by multi-session concurrency and trusting peer-relayed claims instead of direct user confirmation: a shared-git-index race during a simultaneous commit, a duplicated script folder that broke compilation project-wide, two independently-declared FormationType enums colliding by name, and at least one stale 'still missing' gap note written by a session that hadn't cross-checked the actual file tree. The log also shows the project already self-correcting toward better discipline - later entries consistently say 'confirmed directly with the user, not acting on a peer relay alone' before major decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Given this project now has a strict single-session, single-item CLAUDE.md protocol in place, the strongest recommendation here is procedural, not technical: keep running one Claude Code session at a time against this repo going forward, and treat any claim about 'what another session did' as unverified until you or the current session confirms it against the actual repo state - exactly the pattern the log's later entries already converged on independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Still true as of 2026-09-14: CLAUDE.md's own status log records at least one further concurrent-session incident (the branch jumping from 53 to 61 commits ahead of origin mid-session on 2026-09-14, during the UI portrait-staging session) - the guidance above remains current, not historical.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>ROADMAP - ART DIRECTION &amp; ASSET REQUIREMENTS (from docs/Roadmap.md Section 4, retired 2026-09-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Where this overlaps the existing Action Items / Art Generation Prompts sheets (asset-by-asset requirements and Canva/Meshy prompts), this sheet cross-references rather than repeating - see the note on each block. What's here is what those sheets don't already carry: the overall visual-standard target, the civ-by-civ audit findings, and the standing sourcing/creation checklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>4.1 TARGET VISUAL STANDARD - Mid-poly realistic PBR (AoE II:DE / AoE IV visual tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Unit poly count</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>4,000-8,000 tris (readable detail at RTS zoom, not hero-model density)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>Building poly count</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>8,000-20,000 tris depending on tier (House low end, Wonder/TownCenter high end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>Unit texture resolution</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>1024x1024 minimum, PBR (albedo/normal/metallic-roughness)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>Building texture resolution</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>2048x2048-4096x4096, PBR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Material workflow</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Metallic/roughness PBR only - reject any pack still on a Built-in-RP Standard shader without a clean URP conversion path</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>Rig</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>One shared humanoid rig for all human units (already established - keep it), but the rig itself and its base body should be re-evaluated against this standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>Style reference</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Each civ's buildings should read as a distinct real-world architectural tradition - Chola (Dravidian temple, gopuram towers), Vijayanagara (Hampi granite/Deccan), Rajput (fort/haveli, chhatris), Maurya (pillar/stupa motifs), Maratha (Deccan hill-fort) - not just a palette swap on one shared kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>4.2 EXISTING ASSETS - AUDIT AGAINST THE STANDARD (civ-by-civ live audit, 2026-09-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>The building-polycount and civ-style-differentiation headline findings are already summarized on the Dev Status Overview sheet ('WHAT IS FULLY CLOSED' / mesh-decimation Wave item) and Status Index. Findings NOT already captured elsewhere are listed below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>Dev Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>Sample unique unit (Pillar Edict Scholar, Maurya) passes cleanly</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>7,084 tris, 2048 texture, clean Universal Render Pipeline/Lit shader - the reference case for what 'meets the standard' looks like.</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>War Galley (shared naval unit) mixes two shaders on one model</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Some submeshes use URP/Lit, others still use the raw glTFast-generated Shader Graphs/glTF-pbrMetallicRoughness, never converted. Polycount (4,030 tris) is fine. Worth a cleanup pass for consistency, not urgent - doesn't look visually broken.</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Environment props (trees, mines, quarries, farmland) not poly/texture-audited</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Out of the 2026-09-02 audit session's scope, flagged as remaining work for a future pass.</t>
+        </is>
+      </c>
+      <c r="C19" s="57" t="inlineStr">
+        <is>
+          <t>[?] Unclear / needs verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Maurya's TownCenter reads architecturally closer to Mughal/colonial than actual Mauryan-era style</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Visually striking, clearly distinct from the other 4 civs, but a large gilded dome over a colonnaded terrace isn't Ashokan-pillar/stupa/polished-sandstone Mauryan architecture. Authenticity nuance, not a 'looks bad' finding.</t>
+        </is>
+      </c>
+      <c r="C20" s="57" t="inlineStr">
+        <is>
+          <t>[?] Unclear / needs verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>Chola and Vijayanagara TownCenters read as the same architectural family at a glance</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Both are stepped-pyramid gopuram-style temple towers in a near-identical grey-brown stone tone; Vijayanagara's reads as a smaller Chola rather than Hampi's distinct granite Deccan style. Not necessarily worth re-sourcing, but doesn't clear the 'distinct tradition' bar as cleanly as Rajput/Maratha do.</t>
+        </is>
+      </c>
+      <c r="C21" s="57" t="inlineStr">
+        <is>
+          <t>[?] Unclear / needs verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="inlineStr">
+        <is>
+          <t>4.3 ASSET REQUIREMENTS - see Action Items &amp; Art Generation Prompts sheets for the full asset-by-asset table</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>45/45 civ-specific building models (9 types x 5 civs) are complete - see Dev Status Overview 'WHAT IS FULLY CLOSED'. The 2 items below are genuinely still open and not fully covered by the Action Items sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="inlineStr">
+        <is>
+          <t>Dev Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>Per-civ architectural differentiation - overall visual-fidelity gap</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>The single biggest visual-fidelity gap relative to real AoE civs at the time this was written; largely closed by the 45/45 civ-building delivery since, but Section 4.2's Chola/Vijayanagara-similarity and Maurya-authenticity nuances above remain.</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>[R] Superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Zero coverage. See Open Items &amp; Priority sheet's Open Backlog block.</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>4.4 SOURCING/CREATION CHECKLIST (apply to anything new, regardless of source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Verify scale in-Editor, in-scene, next to what it'll actually stand beside - isolated preview has already missed a 4-27x scale error once; don't trust preview alone again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Confirm PBR metallic/roughness workflow before import - reject Built-in-RP-only material sets outright rather than fixing them post-hoc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Check the color/tint property name if civ-color tinting matters (_Color/baseColorFactor/diffuseFactor have all appeared from different sources) - TintMaterials already falls back through all three, but verify a new source actually works before assuming it does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Watch for Z-up sources needing a corrected child transform (not a root-transform fix - the spawn path resets root rotation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Mandatory, per model, before committing: instantiate in-scene and compare against reference concept art from at least a front-on angle, not just an AABB bounds check - a Z-up model lying flat on a wide base can have superficially plausible bounds while still being on its back. For anything in BuildingModelFactory.ImportRotationCorrections (e.g. Tower), a bare instantiate-and-inspect of the saved prefab is NOT sufficient - the dict's correction is applied at runtime on top of whatever's baked into the model, so the check must reproduce the full spawn stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>'Pick the rotation candidate that gives the tallest Y bounds' is not a universal heuristic - only holds for genuinely tall/narrow assets (Towers). A wide, sprawling building (a TownCenter fort complex) can have its correct orientation be shorter than a wrong orientation's bounds. What actually resolves it: read the raw mesh's vertex data directly and compare bottom-band vs. top-band vertex-count ratios per local axis - a real building has far more geometry near its base than its tip. Still confirm the sign and the final result visually against reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>For any body-swap or rig-affecting asset, verify rig compatibility explicitly and in isolation before wiring it into the shared path every unit depends on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Keep unused/source-only import content out of Assets/Resources/ (use Assets/importedmodels/) so it doesn't bloat builds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Every CC-BY (or similar attribution-required) asset gets a CREDITS.md entry at the time it's added - the Sword/Bow/Kanabo/Mounts gap (sourced with no recorded attribution) shows how easily this slips if it's not immediate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION WAVES 0-6 (from docs/IMPLEMENTATION_ROADMAP.md, retired 2026-09-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>The dependency-ordered execution plan: 40 scoped items grouped into Waves 0-6, each sized to one Claude Code session. This is the sheet a future session opens to know 'what's the next scoped, session-sized task.' Waves 0-5 (31 items) are all closed. Wave 6 (9 items) is the open parallel-safe economy/meta backlog - see the Dev Status Overview sheet for the wave-level headline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
+      </c>
+      <c r="C4" s="51" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D4" s="51" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E4" s="51" t="inlineStr">
+        <is>
+          <t>Depends On</t>
+        </is>
+      </c>
+      <c r="F4" s="51" t="inlineStr">
+        <is>
+          <t>Dev Status</t>
+        </is>
+      </c>
+      <c r="G4" s="51" t="inlineStr">
+        <is>
+          <t>Scope / Closure Notes</t>
+        </is>
+      </c>
+      <c r="H4" s="51" t="inlineStr">
+        <is>
+          <t>Source Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Wave 0</t>
+        </is>
+      </c>
+      <c r="C5" s="39" t="inlineStr">
+        <is>
+          <t>Reconcile UnitClass vs UnitCategory</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>Combat/UnitClass.cs (7 values) and UnitDefinition.cs's UnitCategory (9 values) diverged - Support/Hero existed in only one. Collapsed to one shared UnitClass (Combat namespace) used everywhere; global UnitCategory deleted. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Wave 0</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>Verify the retroactive upgrade rule</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F6" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed UpgradeProgress.cs did NOT promote already-spawned units (bonus baked in at spawn). Fixed: Attackable/MeleeAttacker/BoatAttacker now live-read the bonus at damage-resolution time via an opt-in EnableUpgrade*Scaling() call on the 13 factories that already baked it in. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Wave 0</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>Confirm the minimum-damage clamp</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F7" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>Verify-only, no bug found: Attackable.TakeDamage's Mathf.Max(1f, amount-armor) floor is applied last, after armor subtraction and after any CombatBonus multiplier - a stacked armor value plus a sub-1.0 counter multiplier can't silently floor a hit at 0. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Wave 0</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>Wire DamageType.Trample and DamageType.Fire</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Nothing (Fire half blocked on Wave 4's Fire Ship)</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Resolved the DamageType enum duplication (item 1's own prerequisite) - one shared enum (Melee/Pierce/Siege/Fire/Trample) in Combat/Attackable.cs. Trample wired onto both War Elephant factories via SetDamageType + the existing splash mechanism. Fire deliberately deferred to its real consumer, the Fire Ship (Wave 4 item 25, closed 2026-09-05) - Fire is now also live. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>Add AgeId.Durg</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F9" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>AgeId enum gained Durg between Classical and Imperial; new age_profile_template.csv row (250 Wood + 150 Stone, 40s, gather x1.18, HP x1.15, train x0.85). Deliberately no Gold-cost column added (schema has never had one for any age). Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>Age-up building-count requirement</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="F10" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>New Buildings/AgeUpRequirement.cs: 2 completed, non-TownCenter buildings required to age up, gate applies from Classical onward only (Ancient-&gt;Classical stays cost-only). Recomputes fresh from Building.All every call. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>Durg building</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="F11" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>New Buildings/Durg.cs/DurgFactory.cs. User-confirmed: trains unique units (relocated off Barracks), strongest defensive building in the game (GarrisonCapacity 12, 6 max bonus shots, 700 HP/4-6 armor vs TownCenter's 500/3-5). AI-side TryBuildDurg hook added so the AI didn't silently stop training unique units. No bespoke 3D model yet (asset gap, flagged). Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>Karmashala (Blacksmith-equivalent building)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>New Buildings/Karmashala.cs/KarmashalaFactory.cs. Gated to Classical Age; flat Attack/Armor research tracks moved OFF Barracks onto Karmashala entirely. AI-side TryBuildKarmashala hook added. No bespoke 3D model yet (asset gap, flagged). Closed 2026-09-04 - closes Wave 2.</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>Infantry line (5 tiers)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-2</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Padati (base) through 5 tiers. First upgrade-ladder item; research lives on Barracks, baked in at spawn (not retroactive). Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>Spearman line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 pattern</t>
+        </is>
+      </c>
+      <c r="F14" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Bhaladhari -&gt; Trishuladhari -&gt; Maha Trishuladhari, Classical/Durg/Imperial. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>Archer line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 pattern</t>
+        </is>
+      </c>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>Dhanurdhara -&gt; Yantra Dhanurdhara -&gt; Maha Dhanurdhara, Classical/Durg/Imperial. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>Knight/Cavalry line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 pattern</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Ashvarohi -&gt; Maha Ashvarohi (Durg) -&gt; Vir Ashvarohi (Imperial), both upgrade tiers gate on Imperial per spec. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>Elephant line (2 tiers, KoB's own invention)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 pattern</t>
+        </is>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>Gajaroha -&gt; Maha Gajaroha, Durg/Imperial. One shared ElephantLineProgress.cs table read by both Maurya's and Vijayanagara's War Elephant factories. Research lives on Durg (not Barracks), since War Elephants train from Durg. This IS the elephant elite tier - excludes both War Elephant factories from item 16's own list. Closed 2026-09-04.</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Mangonel/Siege line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 pattern</t>
+        </is>
+      </c>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Shilakshepaka -&gt; Maha Shilakshepaka -&gt; Vajra Shilakshepaka, Durg/Imperial/Imperial. Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>Galley/Naval line (3 tiers)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>Item 9 pattern</t>
+        </is>
+      </c>
+      <c r="F19" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>Rana Nauka -&gt; Maha Rana Nauka -&gt; Samrat Nauka, Classical/Durg/Imperial. Research lives on Dock (not Barracks), since War Galley trains from Dock. Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Unique-unit Elite tier (2 tiers x 5 units, was 7 - see item 13)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Item 13</t>
+        </is>
+      </c>
+      <c r="F20" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Keyed by unitId, not CivilizationId (Chola Naval Raider, Rajput Royal Guard, Maurya Pillar Edict Scholar, Maratha Mavla Raider, Maratha Durg Garrison - the 2 War Elephant factories are covered by item 13 instead). Single Imperial-gated step. Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Wave 3</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>Blacksmith-style stat upgrade steps (age-gate Karmashala's 3 tiers)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Item 8</t>
+        </is>
+      </c>
+      <c r="F21" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>Karmashala's UpgradeProgress.MaxTier was already 3 but none of the 3 tiers were age-gated - a Karmashala only needed Classical Age to exist, so all 3 were researchable back-to-back purely gold-limited. Added TierRequiredAges (Classical/Durg/Imperial) to both Attack and Armor tracks. Closed 2026-09-05 - closes Wave 3.</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Scout (Chara), 3-tier line</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1</t>
+        </is>
+      </c>
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>Chara -&gt; Vega Ashvarohi -&gt; Maha Vega Ashvarohi, Ancient/Classical/Durg. Grows vision radius/move speed per tier instead of HP/damage. First live user of UnitClass.Support for real combat classification. No dedicated mount model yet (asset gap, flagged - looks identical to Cavalry). Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>Skirmisher (anti-archer counter-archer), 2 tiers</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1</t>
+        </is>
+      </c>
+      <c r="F23" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>Pratirodhi Dhanurdhara -&gt; Maha Pratirodhi Dhanurdhara, Classical/Durg. Completes the counter web's last gap (2x vs Archer, 1.25x received from Infantry). Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>Battering Ram, 3 tiers</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1</t>
+        </is>
+      </c>
+      <c r="F24" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>Dwarabhanjaka -&gt; Maha Dwarabhanjaka -&gt; Vajra Dwarabhanjaka, Classical/Durg/Imperial. Anti-building ONLY (new MeleeAttacker.SetBuildingOnly - a structural refusal, not a weak multiplier), no splash, garrisonable (own GarrisonPoint, capacity 4). Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>Cavalry Archer, 2 tiers</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1</t>
+        </is>
+      </c>
+      <c r="F25" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>Ashva Dhanurdhara -&gt; Maha Ashva Dhanurdhara, Durg/Imperial. Classified as UnitClass.Archer (mounted Archer, not a new counter archetype) with Cavalry's move speed. Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>Camel Rider, 2 tiers (design decision first)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1, user yes/no</t>
+        </is>
+      </c>
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>Ushtrarohi -&gt; Maha Ushtrarohi, Durg/Imperial. User confirmed build via AskUserQuestion. New UnitClass.Camel (Spearman's anti-Cavalry role + Cavalry's move speed). No dedicated camel mount model yet (asset gap, flagged). Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>Scorpion, 2 tiers</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1</t>
+        </is>
+      </c>
+      <c r="F27" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>Bana Yantra -&gt; Maha Bana Yantra, Durg/Imperial. New MeleeAttacker.SetPierceThrough(depth) - a real line-segment pass-through-damage path (not a Physics raycast, deterministic for lockstep), new UnitClass.Scorpion (2x vs Infantry, 1.5x received from Cavalry). No dedicated siege-engine model yet (asset gap, flagged). Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>Trebuchet, 1 tier</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1</t>
+        </is>
+      </c>
+      <c r="F28" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>Maha Yantra, Imperial only, long-range (10) with a minimum range (4, new MeleeAttacker.SetMinRange - a target too close can't be fired on at all). First live consumer of DamageType.Siege. Closed 2026-09-07 - closes Wave 4 (11/11 items).</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>Fire Ship, 3 tiers</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>Wave 0 item 4, Wave 1</t>
+        </is>
+      </c>
+      <c r="F29" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>Agni Nauka -&gt; Maha Agni Nauka -&gt; Vega Agni Nauka, Classical/Durg/Imperial. First real consumer of DamageType.Fire. New UnitClass.FireShip (2x hard counter vs Naval). Reuses the War Galley hull with a fire-orange tint (asset gap, flagged - partial differentiator only). Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>Trader (land + naval), design decision first</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Waves 0-1, user yes/no</t>
+        </is>
+      </c>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>Vanik (land) / Trade Ship (naval). User confirmed full scope (both variants) via AskUserQuestion. New Resources/Trader.cs/BoatTrader.cs shuttle between owned/allied Markets/Docks paying distance-scaled Gold per leg. Both units completely unarmed. Vanik trains at Market (new training queue added there), Trade Ship at Dock. Not built: trading with enemy/unallied Markets, route-line VFX, AI-side use. Closed 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>Support units - Vaidya (healer) and Purohita (converter)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>Wave 0 item 1, Wave 2 item 7</t>
+        </is>
+      </c>
+      <c r="F31" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>Splits AoE's Monk into two units. New Buildings/Monastery.cs trains both (new building, user-confirmed via AskUserQuestion over reusing Durg/Karmashala). Purohita's conversion is a full AoE-style per-second chance roll scaled by missing-HP%, using DeterministicRandom for lockstep safety. No AI-side use. Closed 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Wave 4</t>
+        </is>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>Hero unit - Maharaja, per civ</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>A confirmed victory condition first</t>
+        </is>
+      </c>
+      <c r="F32" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>Built together with Regicide (pulled forward from Wave 6 item 37). 3 AskUserQuestion rounds confirmed: build both this session; Maharaja is the STRONGEST unit in the game (not AoE's defenseless King); Regicide is an opt-in GameSettings.RegicideEnabled toggle, off by default; a dead Maharaja is retrainable once Regicide is off. New Progression/HeroProgress.cs, Combat/MaharajaFactory.cs (stat-identical across all 5 civs), new UnitClass.Hero. No dedicated model (reuses Royal Guard's Human+Horse+Sword combo, asset gap flagged). Closed 2026-09-07.</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Wave 5</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>Player/team colour system</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F33" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>Building side: TeamColorBuildingTint.cs bakes a metallic-mask trim tint (RenderTexture blit, cached per albedo+metallic+faction combo) - shipped and live-verified, piloted on Chola then swept across all 45 buildings (buildings with no metallic map, e.g. Vijayanagara's set, fall back to the existing pennant/banner). Unit side: banners/pennants (Core/TeamColorAccent.cs) shipped 2026-09-07; a further unit-body accent tint (Core/TeamColorUnitTint.cs) exists only as an UNCOMMITTED pilot in the working tree as of 2026-09-14, blocked on Blender-painted UV masks per docs/TEAM_COLOR_ART_BRIEF.md (unit textures are UV atlases with no 2D spatial coherence, so no 2D/AI image tool can produce an aligned mask).</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Wave 5</t>
+        </is>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>UI layout re-anchor - bottom bar</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F34" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>Re-anchored BuildMenu/SelectedUnitPanel/a ResourceHUD slice into one shared bottom-docked bar (command panel / info panel / minimap, left to right), replacing the prior floating/scattered layout. Closed 2026-09-05.</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Wave 5</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>BuildMenu command-panel grid redesign</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>Item 30</t>
+        </is>
+      </c>
+      <c r="F35" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>Replaced the ~56-button vertical stack with a true icon grid (4 columns), a new hover-tooltip system for the 35 icon-less buttons, and Prev/Next pagination for overflow contexts. Closed 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Wave 5</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>Age/research always-visible readout</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>Item 30</t>
+        </is>
+      </c>
+      <c r="F36" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>Top-center current Age name + research-in-progress meter. Deliberately scoped to Age-up research only (not every concurrent research track). New TownCenter.FindAgingUp; ResourceHUD gained a second row (label + fill bar, hidden by default). Closed 2026-09-14 - closes Wave 5 (all 3 items, and Wave 5's own exit criteria: every unit/building has a working team-colour slot, HUD reads as one coherent bottom-bar layout).</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C37" s="39" t="inlineStr">
+        <is>
+          <t>Town Bell</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F37" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>One-click garrison-all-workers: static TownBell.Ring(FactionId) finds every TownCenter and every Worker owned by that faction and orders each to the nearest TownCenter with room, cancelling in-progress worker tasks first. New global BuildMenu.townBellButton + F8 hotkey. Found and fixed a real latent bug along the way: GarrisonSeeker cached its UnitMover sibling eagerly in Awake() instead of lazily, unlike every sibling class. Closed 2026-09-14 - first Wave 6 item closed.</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>Idle-worker indicator</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Item 30 if inside the new bottom bar, otherwise independent</t>
+        </is>
+      </c>
+      <c r="F38" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>Small UI addition near the minimap.</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="inlineStr">
+        <is>
+          <t>Relics + Monastery-equivalent, if wanted</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>A yes/no design decision; Wave 4 item 27 if the carrier is Vaidya/Purohita</t>
+        </is>
+      </c>
+      <c r="F39" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>AoE II relics pay 0.5 gold/sec and can trigger a victory countdown - needs a carrier unit and a building to store them in.</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C40" s="39" t="inlineStr">
+        <is>
+          <t>Score system</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>Nothing (higher value once Waves 3-4 give it more to score)</t>
+        </is>
+      </c>
+      <c r="F40" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>Four weighted categories (Military/Economy/Technology/Society), modeled on AoE II's own weighting.</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="inlineStr">
+        <is>
+          <t>Victory conditions beyond Conquest</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>A design decision on whether Wonder/Relic are wanted at all</t>
+        </is>
+      </c>
+      <c r="F41" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>Time Limit and Regicide are BOTH closed (Regicide pulled forward into Wave 4 item 28's own session, 2026-09-07, opt-in via GameSettings.RegicideEnabled). Wonder and Relic victory conditions remain unbuilt - building all of AoE's victory conditions is not automatically the right scope for this project, flagged as a decision, not an oversight.</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>Game modes</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Item 37 if modes are tied to specific victory conditions</t>
+        </is>
+      </c>
+      <c r="F42" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>Selectable Skirmish/Deathmatch/Regicide-style/Empire-Wars-style modes on top of the scenario system that already exists.</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>Cheat codes</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F43" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>Low priority, genuinely useful for testing your own scenarios.</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6</t>
+        </is>
+      </c>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>Tutorial content</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>Nothing (higher value once more of the roster exists)</t>
+        </is>
+      </c>
+      <c r="F44" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>Rides the existing MissionObjective/MissionTrigger system - pure content authoring, no new system needed.</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>40b</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Wave 6 (asset-blocked)</t>
+        </is>
+      </c>
+      <c r="C45" s="39" t="inlineStr">
+        <is>
+          <t>Soundtrack</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>Nothing (your asset-sourcing task)</t>
+        </is>
+      </c>
+      <c r="F45" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>Self-serve CC0 tracks from Kenney.nl, same sourcing approach as the existing Audio/SfxPlayer.cs pass. Claude Code's role is limited to wiring whatever tracks you provide, not composing. Note: the source doc numbered this item '40' a second time (a duplicate of Tutorial's own number) - preserved here as '40b' to avoid collision, not renumbered.</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>Implementation Waves 0-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="50" t="inlineStr">
+        <is>
+          <t>ASSET-BLOCKED TRACK (runs alongside all waves, on your schedule - your work or a commissioned artist's, not a coding session's)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B48" s="51" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>Dev Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>Villager (Praja) art</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>Currently an unclothed generic humanoid (the shared Human Character Dummy body). Given the Worker is the unit a player looks at most, may be worth resourcing ahead of combat-unit art.</t>
+        </is>
+      </c>
+      <c r="E49" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Town Center age-variants (4 ages x 5 civs)</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Shipped 2026-09-04 as part of the Age-aware building visuals session: Ancient/Classical are one shared model each, Durg is civ-specific (5 models), Imperial reuses the existing civ-specific model. Age-up re-skins are retroactive (every standing building rebuilds in place).</t>
+        </is>
+      </c>
+      <c r="E50" s="52" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>Tower and Wall upgrade tiers</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Tower/Wall follow the OPPOSITE civ-differentiation pattern from every other building (civ-specific only at Imperial; Ancient/Classical/Durg are one shared model per tier). Age-tiered visuals shipped in the same 2026-09-04 session. A true per-tier UPGRADE-tier system for buildings (analogous to the unit tier ladders in Wave 3) was never scoped or built - flagged in the source doc as a 'Wave 3.5 candidate' if wanted.</t>
+        </is>
+      </c>
+      <c r="E51" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="inlineStr">
+        <is>
+          <t>Drop-off building art (Lumber Camp / Mining Camp / Mill)</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Currently procedural silhouettes (log-pile shed, ore-heap shed, stilted granary), visibly below the bar the other 45 buildings set.</t>
+        </is>
+      </c>
+      <c r="E52" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>Per-civ unit gear (helmet/shield/weapon variants)</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>WeaponAttachment.cs's hand-bone system already exists; only the art is missing.</t>
+        </is>
+      </c>
+      <c r="E53" s="55" t="inlineStr">
+        <is>
+          <t>[X] Blocked / Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>New-unit models for every Wave 4 item</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Scout, Skirmisher, Battering Ram, Cavalry Archer, Camel Rider, Scorpion, Trebuchet, Fire Ship, Trader, Vaidya/Purohita, Maharaja - every one of these currently reuses an existing body/prop combo rather than having distinct art (each flagged individually in its own row above).</t>
+        </is>
+      </c>
+      <c r="E54" s="56" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B51:D51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -31129,7 +31129,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. Two items this sheet previously listed as open turned out already closed once checked directly against the repo on 2026-09-14 (portrait display wiring - commit 42a5a2c; the Maurya/Maratha UniqueTechDefinition crash - commit 6c3d21c, with regression tests) - a reminder to verify status against Assets/Scripts before starting, not just this sheet. The natural remaining candidates: (1) pick up Wave 6's decision-free items - idle-worker indicator, cheat codes, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) refresh the confirmed-stale README; (4) unit-side team colour once Blender masks are sourced.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. Two items this sheet previously listed as open turned out already closed once checked directly against the repo on 2026-09-14 (portrait display wiring - commit 42a5a2c; the Maurya/Maratha UniqueTechDefinition crash - commit 6c3d21c, with regression tests). README.md was refreshed the same day (rewritten from the stale single-map/one-generic-civ prototype description to reflect the actual current project). The natural remaining candidates: (1) pick up Wave 6's decision-free items - idle-worker indicator, cheat codes, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
         </is>
       </c>
     </row>
@@ -34123,12 +34123,12 @@
       </c>
       <c r="D31" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>The root README.md still describes the original single-map/3-civ/no-naval prototype scope and stops its milestone list at 26 - confirmed badly stale 2026-09-03. Pure doc-writing, zero blocker.</t>
+          <t>Closed 2026-09-14. Rewritten to reflect the actual current project (5 civs, 4 Ages, ~25-type unit roster with tier ladders, naval, diplomacy, scenario editor with LAN play, LAN multiplayer MVP) instead of the original single-map/one-generic-civ/no-naval prototype.</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -34492,12 +34492,12 @@
       </c>
       <c r="D46" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="E46" s="22" t="inlineStr">
         <is>
-          <t>Confirmed stale 2026-09-03; stops its own milestone list at item 26.</t>
+          <t>Closed 2026-09-14 - see row 31 above for detail.</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30305,7 +30305,7 @@
     <row r="5" ht="74" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave, and 1 of its 9 items (Town Bell) is done. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Development is now in a long tail of optional systems (Score, game modes, relics, tutorial, music, cheat codes), UI/art polish, and asset sourcing - not core mechanics.</t>
+          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave, and 2 of its 9 items (Town Bell, idle-worker indicator) are done. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Development is now in a long tail of optional systems (Score, game modes, relics, tutorial, music, cheat codes), UI/art polish, and asset sourcing - not core mechanics.</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -30533,7 +30533,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>OPEN. Item 33 Town Bell closed 2026-09-14. Remaining: idle-worker indicator (34), Relics + relic storage (35), Score system (36), Wonder/Relic victory conditions (37), game modes (38), cheat codes (39), tutorial content (40), soundtrack.</t>
+          <t>OPEN. Items 33 (Town Bell) and 34 (idle-worker indicator) closed 2026-09-14. Remaining: Relics + relic storage (35), Score system (36), Wonder/Relic victory conditions (37), game modes (38), cheat codes (39), tutorial content (40), soundtrack.</t>
         </is>
       </c>
     </row>
@@ -30887,7 +30887,7 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Wave 6 backlog - 8 of 9 items still open, all parallel-safe. The three needing no design decision are the idle-worker indicator, cheat codes and tutorial content.</t>
+          <t>- Wave 6 backlog - 7 of 9 items still open, all parallel-safe. The two remaining with no design decision are cheat codes and tutorial content.</t>
         </is>
       </c>
     </row>
@@ -31129,7 +31129,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. Two items this sheet previously listed as open turned out already closed once checked directly against the repo on 2026-09-14 (portrait display wiring - commit 42a5a2c; the Maurya/Maratha UniqueTechDefinition crash - commit 6c3d21c, with regression tests). README.md was refreshed the same day (rewritten from the stale single-map/one-generic-civ prototype description to reflect the actual current project). The natural remaining candidates: (1) pick up Wave 6's decision-free items - idle-worker indicator, cheat codes, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. Two items this sheet previously listed as open turned out already closed once checked directly against the repo on 2026-09-14 (portrait display wiring - commit 42a5a2c; the Maurya/Maratha UniqueTechDefinition crash - commit 6c3d21c, with regression tests). README.md was refreshed the same day, and Wave 6 item 34 (idle-worker indicator) was closed the same day too. The natural remaining candidates: (1) pick up another Wave 6 decision-free item - cheat codes, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
         </is>
       </c>
     </row>
@@ -33192,6 +33192,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="50" t="inlineStr">
         <is>
@@ -34177,6 +34178,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="50" t="inlineStr">
         <is>
@@ -34191,6 +34193,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="50" t="inlineStr">
         <is>
@@ -34552,7 +34555,7 @@
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Wave 6 backlog items 34-40 (idle-worker indicator, Relics, Score, Wonder/Relic victory conditions, game modes, cheat codes, tutorial, soundtrack)</t>
+          <t>Wave 6 backlog items 35-40 (Relics, Score, Wonder/Relic victory conditions, game modes, cheat codes, tutorial, soundtrack)</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
@@ -34567,7 +34570,7 @@
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>See the Implementation Waves 0-6 sheet for the full per-item breakdown. Item 33 (Town Bell) is the only Wave 6 item closed so far (2026-09-14).</t>
+          <t>See the Implementation Waves 0-6 sheet for the full per-item breakdown. Items 33 (Town Bell) and 34 (idle-worker indicator) are the only Wave 6 items closed so far (both 2026-09-14).</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
@@ -36587,12 +36590,12 @@
       </c>
       <c r="F38" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
         <is>
-          <t>Small UI addition near the minimap.</t>
+          <t>New UI/IdleWorkerFinder.cs (pure FindAll(FactionId) over Unit.All, Gatherer-marker + UnitStatus.IsIdle) and UI/IdleWorkerIndicator.cs (self-attached to MinimapController via AddComponent, no scene wiring): a live "Idle Workers: N" panel above the minimap; click or F6 selects the next idle worker round-robin and pans the camera, same as AoE's own idle-villager button. Found and fixed a real live bug: MinimapController.ApplyDiamondFrame() reparents/re-stretches its own RectTransform, so the indicator has to read a pre-diamond-frame snapshot, not `transform` itself. 6 new tests (528 total). Closed 2026-09-14.</t>
         </is>
       </c>
       <c r="H38" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30295,6 +30295,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -30314,6 +30315,7 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -30537,6 +30539,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -30676,6 +30679,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -30807,6 +30811,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -30870,6 +30875,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
@@ -30887,13 +30893,14 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Wave 6 backlog - 7 of 9 items still open, all parallel-safe. The two remaining with no design decision are cheat codes and tutorial content.</t>
+          <t>- Wave 6 backlog - 6 of 9 items still open. Item 39 (Cheat codes) was built 2026-09-15 but is NOT yet live-verified (MCP servers unreachable that session) - treat it as code-complete, not closed, until a test run + live check happens. The two remaining with no design decision are Score system (36) and tutorial content (40).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="22" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -31088,6 +31095,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
@@ -31119,6 +31127,7 @@
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="22" t="n"/>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
@@ -31129,7 +31138,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. Two items this sheet previously listed as open turned out already closed once checked directly against the repo on 2026-09-14 (portrait display wiring - commit 42a5a2c; the Maurya/Maratha UniqueTechDefinition crash - commit 6c3d21c, with regression tests). README.md was refreshed the same day, and Wave 6 item 34 (idle-worker indicator) was closed the same day too. The natural remaining candidates: (1) pick up another Wave 6 decision-free item - cheat codes, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. Wave 6 item 39 (Cheat codes) was picked up 2026-09-15 but needs a follow-up test run + live UnityMCP verification before it counts as closed (both MCP servers were unreachable that session). The natural remaining candidates: (1) verify item 39, then pick up another Wave 6 decision-free item - Score system, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
         </is>
       </c>
     </row>
@@ -33192,7 +33201,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="50" t="inlineStr">
         <is>
@@ -34178,7 +34186,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="50" t="inlineStr">
         <is>
@@ -34193,7 +34200,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="50" t="inlineStr">
         <is>
@@ -36790,12 +36796,12 @@
       </c>
       <c r="F43" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[~] Partial - built, not live-verified</t>
         </is>
       </c>
       <c r="G43" s="22" t="inlineStr">
         <is>
-          <t>Low priority, genuinely useful for testing your own scenarios.</t>
+          <t>New Core/CheatCommandParser.cs (pure parser) + Core/CheatCodes.cs (executor, always targets FactionId.Player): resources/wood/food/gold/stone &lt;n&gt;, age &lt;name&gt;, reveal, spawn &lt;unitType&gt; [count], win, lose, help. New UI/CheatConsole.cs (BackQuote hotkey, Quake-style typed console), refuses to run while NetworkMatch.IsActive. Added FogOfWarManager.ToggleRevealAll() and MatchManager.ForceOutcome() as the two small public hooks neither had before. 17 new EditMode tests (Spawn execution not exercised - EntitySpawner hard-errors outside Play mode, same as every other factory caller). NOT LIVE-VERIFIED (2026-09-15) - both unity/UnityMCP MCP servers were unreachable this session despite a real Editor + bridge process running; code was read back against every real API it touches but the EditMode suite was never actually run. Needs a follow-up test run + live verification before being treated as fully closed like every other Wave 6 item.</t>
         </is>
       </c>
       <c r="H43" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30295,7 +30295,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -30306,7 +30305,7 @@
     <row r="5" ht="74" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave, and 2 of its 9 items (Town Bell, idle-worker indicator) are done. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Development is now in a long tail of optional systems (Score, game modes, relics, tutorial, music, cheat codes), UI/art polish, and asset sourcing - not core mechanics.</t>
+          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave; 4 of its 9 items (Town Bell, idle-worker indicator, cheat codes, Score system) are done. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Development is now in a long tail of optional systems (game modes, relics, tutorial, music), UI/art polish, and asset sourcing - not core mechanics.</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -30315,7 +30314,6 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -30520,7 +30518,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Economy / meta backlog (parallel-safe, pick any order)</t>
+          <t>OPEN. Items 33 (Town Bell), 34 (idle-worker indicator), 36 (Score system), and 39 (cheat codes) closed. Remaining: Relics + relic storage (35), Wonder/Relic victory conditions (37), game modes (38), tutorial content (40), soundtrack.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -30539,7 +30537,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -30679,7 +30676,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -30811,7 +30807,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -30875,7 +30870,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
@@ -30893,14 +30887,13 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Wave 6 backlog - 6 of 9 items still open. Item 39 (Cheat codes) was built 2026-09-15 but is NOT yet live-verified (MCP servers unreachable that session) - treat it as code-complete, not closed, until a test run + live check happens. The two remaining with no design decision are Score system (36) and tutorial content (40).</t>
+          <t>- Wave 6 backlog - 4 of 9 items still open with no design decision needed: game modes (38, gated on item 37's own decision), tutorial content (40). Item 36 (Score system) closed 2026-09-15 right after item 39's live-verification gap was closed - also found and fixed a real, previously-unnoticed bug while verifying it: GameOverScreen's own root GameObject was saved inactive in the scene, so the entire Victory/Defeat/Draw screen had never actually shown in a real match before this session.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="22" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -31095,7 +31088,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
@@ -31127,7 +31119,6 @@
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="22" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
@@ -31138,7 +31129,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. Wave 6 item 39 (Cheat codes) was picked up 2026-09-15 but needs a follow-up test run + live UnityMCP verification before it counts as closed (both MCP servers were unreachable that session). The natural remaining candidates: (1) verify item 39, then pick up another Wave 6 decision-free item - Score system, tutorial content; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15: item 39 (Cheat codes) was live-verified, and item 36 (Score system) closed the same session, including a real GameOverScreen activation bug fix found while verifying it. Natural remaining candidates: (1) tutorial content (40), the last decision-free item; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
         </is>
       </c>
     </row>
@@ -36676,12 +36667,12 @@
       </c>
       <c r="F40" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>Four weighted categories (Military/Economy/Technology/Society), modeled on AoE II's own weighting.</t>
+          <t>Four weighted categories modeled on AoE II's own split (not a byte-for-byth port of its real, undocumented weights): Military = kills*3 + buildings razed*5 + living combat units*1; Economy = current stockpile total*0.05 + worker count*3 (a live-computed proxy, not a lifetime-gathered total - no single choke point exists across Gatherer/Farm/LivestockWorker/Trader/BoatTrader for that); Technology = Age ordinal*30 + flat Attack/Armor tiers*15 + unique tech researched?50:0 (deliberately doesn't sum the 11 separate per-unit-class tier-line classes - a real future refinement); Society = Population*4 + complete buildings*3 (Wonders/Relics don't exist yet, item 35). New Progression/ScoreProgress.cs: 'recompute, don't track' for every category except kills/razings, the one thing a live scan genuinely can't reconstruct after a unit dies - credited from a new hook in Attackable.TakeDamage's death branch (crediting the attacker, not the victim). New ScoreProgress.Reset() wired into CivilizationSetup.BeginMatchCore alongside DiplomacyRegistry.Reset()/TeamColorBuildingTint.Reset(). GameOverScreen.cs gained a code-built score-breakdown label (Player vs Enemy) shown alongside the existing Victory/Defeat/Draw title - avoids the recurring 'new [SerializeField] null in scene' gotcha. **Found and fixed a real, previously-unnoticed bug while live-verifying, not caused by this item**: GameOverScreen's own root GameObject was saved m_IsActive=0 in the scene - its Awake()/Update() never ran at all, so the entire Victory/Defeat/Draw screen had never actually shown in a real match before this session (only its child 'Panel' was ever meant to toggle). Fixed by activating the GameObject and re-saving the scene. 22 new EditMode tests (ScoreProgressTests.cs), 577/577 total (2 pre-existing, unrelated BuildingModelFactoryTests failures, the standing baseline). Live-verified via UnityMCP through the real production path: a real match, the live formula matched hand-computed expectations exactly against real starting state (Maurya's Classical-age start bonus, 4 starting workers, 1 TownCenter); a real lethal Attackable.TakeDamage call correctly credited the attacker's faction with +1 kill / +1 razing; forcing MatchManager.ForceOutcome(Victory) now shows a real, correctly-laid-out score panel (Military 4 vs 0, Economy 12 vs 12, Technology 30 vs 0, Society 23 vs 19, Total 69 vs 31) with no clipping/overlap, screenshot-confirmed. Deliberately compares Player vs Enemy only, not the optional 3rd faction. Closed 2026-09-15.</t>
         </is>
       </c>
       <c r="H40" s="22" t="inlineStr">
@@ -36796,12 +36787,12 @@
       </c>
       <c r="F43" s="56" t="inlineStr">
         <is>
-          <t>[~] Partial - built, not live-verified</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="G43" s="22" t="inlineStr">
         <is>
-          <t>New Core/CheatCommandParser.cs (pure parser) + Core/CheatCodes.cs (executor, always targets FactionId.Player): resources/wood/food/gold/stone &lt;n&gt;, age &lt;name&gt;, reveal, spawn &lt;unitType&gt; [count], win, lose, help. New UI/CheatConsole.cs (BackQuote hotkey, Quake-style typed console), refuses to run while NetworkMatch.IsActive. Added FogOfWarManager.ToggleRevealAll() and MatchManager.ForceOutcome() as the two small public hooks neither had before. 17 new EditMode tests (Spawn execution not exercised - EntitySpawner hard-errors outside Play mode, same as every other factory caller). NOT LIVE-VERIFIED (2026-09-15) - both unity/UnityMCP MCP servers were unreachable this session despite a real Editor + bridge process running; code was read back against every real API it touches but the EditMode suite was never actually run. Needs a follow-up test run + live verification before being treated as fully closed like every other Wave 6 item.</t>
+          <t>New Core/CheatCommandParser.cs (pure parser) + Core/CheatCodes.cs (executor, always targets FactionId.Player): resources/wood/food/gold/stone &lt;n&gt;, age &lt;name&gt;, reveal, spawn &lt;unitType&gt; [count], win, lose, help. New UI/CheatConsole.cs (BackQuote hotkey, Quake-style typed console), refuses to run while NetworkMatch.IsActive. Added FogOfWarManager.ToggleRevealAll() and MatchManager.ForceOutcome() as the two small public hooks neither had before. 17 new EditMode tests. LIVE-VERIFIED 2026-09-15 (follow-up session, same day): the prior session's MCP unreachability was its own client issue, not a dead bridge - confirmed the bridge process was alive and reachable via a direct curl to its HTTP endpoint, then reconnected via ToolSearch. EditMode suite ran clean: 528/528 (2 pre-existing, unrelated BuildingModelFactoryTests failures, the standing baseline). Found and fixed a real stale-compiled-assembly gap during verification: KingdomsOfBharat.Runtime.dll on disk predated the Cheat*.cs source files by ~14 hours (a prior session had never triggered a real recompile) - forced one via refresh_unity(mode=force, compile=request), confirmed the dll's timestamp/size changed and Cheat* types then resolved in Play mode. Live-verified via UnityMCP through the real production path: a real match (CivilizationSetup.BeginMatch(Maurya)), the real CheatConsole panel opened and every command invoked through the real private OnSubmit method (not a shortcut): wood 500 correctly added to the real ResourceStockpile (0-&gt;500), help printed the command list, reveal flipped FogOfWarManager's real _revealAll flag true, spawn worker 3 added 3 real units to Unit.All (8-&gt;11), age imperial advanced AgeProgress.CurrentAge(Player) from Classical to Imperial, win/lose both correctly set MatchManager.Outcome via ForceOutcome, an unrecognized command returned 'Unknown command: ...', and - the safety-critical case - forcing NetworkMatch.IsActive true via reflection correctly refused a wood grant with zero stockpile mutation and the disabled-during-LAN message. Screenshotted the real in-game console panel rendering cleanly against the HUD with no overlap. This closes item 39 the same way every other Wave 6 item has been closed.</t>
         </is>
       </c>
       <c r="H43" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30305,7 +30305,7 @@
     <row r="5" ht="74" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave; 4 of its 9 items (Town Bell, idle-worker indicator, cheat codes, Score system) are done. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Development is now in a long tail of optional systems (game modes, relics, tutorial, music), UI/art polish, and asset sourcing - not core mechanics.</t>
+          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave; 5 of its 9 items (Town Bell, idle-worker indicator, cheat codes, Score system, tutorial content) are done - every decision-free item is now closed. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Remaining Wave 6 items (Relics, Wonder/KotH victory conditions, game modes) all need a design decision first; otherwise development is a long tail of UI/art polish and asset sourcing.</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>OPEN. Items 33 (Town Bell), 34 (idle-worker indicator), 36 (Score system), and 39 (cheat codes) closed. Remaining: Relics + relic storage (35), Wonder/Relic victory conditions (37), game modes (38), tutorial content (40), soundtrack.</t>
+          <t>OPEN, but every decision-free item is now closed: 33 (Town Bell), 34 (idle-worker indicator), 36 (Score system), 39 (cheat codes), 40 (Tutorial content) are all done. Remaining 3 items (Relics + relic storage (35), Wonder/Relic victory conditions (37), game modes (38)) all need a design decision first, plus soundtrack.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -30887,7 +30887,7 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Wave 6 backlog - 4 of 9 items still open with no design decision needed: game modes (38, gated on item 37's own decision), tutorial content (40). Item 36 (Score system) closed 2026-09-15 right after item 39's live-verification gap was closed - also found and fixed a real, previously-unnoticed bug while verifying it: GameOverScreen's own root GameObject was saved inactive in the scene, so the entire Victory/Defeat/Draw screen had never actually shown in a real match before this session.</t>
+          <t>- Wave 6 backlog - every decision-free item is closed as of 2026-09-15 (item 40, Tutorial content, closed the same session as item 36). The 3 remaining open items all need a design decision before any code work: whether Relics/a relic-storage building are wanted at all (35), whether Wonder/KotH victory conditions are wanted (37, gates 38's game modes too).</t>
         </is>
       </c>
     </row>
@@ -31129,7 +31129,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15: item 39 (Cheat codes) was live-verified, and item 36 (Score system) closed the same session, including a real GameOverScreen activation bug fix found while verifying it. Natural remaining candidates: (1) tutorial content (40), the last decision-free item; (2) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (3) unit-side team colour once Blender masks are sourced.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15, every decision-free Wave 6 item is closed (Town Bell, idle-worker indicator, cheat codes, Score system, Tutorial content). What's left: (1) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (2) unit-side team colour once Blender masks are sourced; (3) UI/art polish or further balance passes, user's call.</t>
         </is>
       </c>
     </row>
@@ -36827,12 +36827,12 @@
       </c>
       <c r="F44" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>Rides the existing MissionObjective/MissionTrigger system - pure content authoring, no new system needed.</t>
+          <t>New CSV-authored mission 'The First Lesson' (tutorial_basics), riding the existing MissionCsvLoader/MissionObjective/MissionTrigger/ScenarioManager system per this item's own roadmap text - no new system needed, purely 3 new rows added to the existing mission_definitions/mission_objectives/mission_triggers CSVs. 5 objectives, one of each existing ObjectiveKind (teaching gather/build/grow-population/hold-ground/attack): ResourceThreshold (Gather 100 Wood), BuildingCountThreshold (Build a House), PopulationThreshold (Grow population to 6), SurviveSeconds (Hold ground 90s), DestroyScriptedTarget (destroy a practice Barracks spawned near the player's own base, not the enemy's, for an easy first combat lesson). Player=Maurya (its 'Houses cost no Wood' bonus and Classical-age start both pair naturally with the lesson content), AI=Maratha, Map=RiverValley. One GrantResourceAtTime trigger (100 Gold at t=20s) proves the trigger pipeline is exercised too. **Found and fixed a real, previously-unnoticed cosmetic bug while authoring this**: ObjectivePanel.cs's box was a fixed 140-tall rect, sized for the 3 original hand-coded missions' single-objective checklists - a 5-objective mission (this tutorial is the first mission in the project with more than 1 objective) would have overflowed it by ~22 units with no mask to clip it. Fixed by having the panel grow to fit its actual row count (Mathf.Max(140, header + rows*26 + margin)), same 'resize to content' precedent SelectedUnitPanel/BuildMenu already established elsewhere - a small, generic, low-risk UI fix, not new game logic. 3 new EditMode tests (TutorialMissionTests.cs) - unlike MissionCsvLoaderTests.cs/MissionRowsTests.cs (which drive the interpreter with synthetic in-memory CSV strings), these are the project's first tests to exercise the REAL Resources-loaded mission CSV files directly (MissionCsvLoader.LoadAll()/ReadCsv against the actual files on disk), catching the class of real formatting mistake (a bad quote, a stray comma, a mis-typed enum) that synthetic tests can't. 580/580 EditMode tests pass (2 pre-existing, unrelated BuildingModelFactoryTests failures, the standing baseline). Live-verified via UnityMCP through the real production path: a real match (CivilizationSetup.BeginScenarioMatch against the real tutorial_basics ScenarioDefinition, not a synthetic one), the real ObjectivePanel rendered all 5 lessons with the grown box and no overflow, the real MissionToast showed the FlavorText on mission start; granting 100 Wood, spawning 2 Workers (population 4-&gt;6... wait 7 with a soldier), completing a real House, and killing a real spawned 'practice Barracks' via a real Attackable.TakeDamage call each flipped their objective to complete (strikethrough, confirmed by screenshot) and fired the matching MissionToast CompleteText; the real trigger correctly granted 100 Gold at t=20s (screenshot-confirmed non-zero Gold); MatchManager.Outcome correctly stayed Ongoing with 4/5 objectives complete, confirming the AND-across-all-objectives victory logic (previously only ever exercised by single-objective missions) works correctly for a genuinely multi-objective mission for the first time. The 5th objective (SurviveSeconds) was not run to its full 90-second completion live (a deliberate scoping call, not a gap - it shares the exact code path DefendHampi's own SurviveSeconds objective already uses and has its own dedicated passing unit test). Closed 2026-09-15 - this closes the last decision-free Wave 6 item; remaining Wave 6 items all need a design decision first (Relics, Wonder/KotH victory conditions, game modes).</t>
         </is>
       </c>
       <c r="H44" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30887,7 +30887,7 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>- Wave 6 backlog - every decision-free item is closed as of 2026-09-15 (item 40, Tutorial content, closed the same session as item 36). The 3 remaining open items all need a design decision before any code work: whether Relics/a relic-storage building are wanted at all (35), whether Wonder/KotH victory conditions are wanted (37, gates 38's game modes too).</t>
+          <t>- Wave 6 backlog - every decision-free item is closed as of 2026-09-15 (item 40, Tutorial content, closed the same session as item 36). The 3 remaining open items' design decision was RESOLVED 2026-09-15 (AskUserQuestion, no code written this session): build Relics + Monastery collection (35, economic gold-trickle only, no new victory condition), Deathmatch + King of the Hill game modes (38, KotH IS a new victory condition - see 37), Wonder is explicitly DECLINED (37 stays partial - Time Limit + Regicide closed, Wonder/Relic-victory closed-as-declined, KotH open). Each of Relics/Monastery, Deathmatch, and KotH is its own future one-item-per-session pickup.</t>
         </is>
       </c>
     </row>
@@ -31074,7 +31074,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Relics, Wonder and King-of-the-Hill victory conditions, game modes</t>
+          <t>Relics + Monastery (35), Deathmatch (38), King of the Hill (37/38) - all scoped 2026-09-15, none implemented yet</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -31129,7 +31129,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15, every decision-free Wave 6 item is closed (Town Bell, idle-worker indicator, cheat codes, Score system, Tutorial content). What's left: (1) resolve the design decisions gating Relics, Wonder/KotH victory conditions and game modes; (2) unit-side team colour once Blender masks are sourced; (3) UI/art polish or further balance passes, user's call.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15, every decision-free Wave 6 item is closed (Town Bell, idle-worker indicator, cheat codes, Score system, Tutorial content), AND the Relics/Wonder/game-modes design decision is now resolved (Relics+Monastery economic-only, Deathmatch, King of the Hill; Wonder declined). What's left: (1) implement Relics + Monastery collection (35); (2) implement Deathmatch mode (38); (3) implement King of the Hill zone-control victory (37/38); (4) unit-side team colour once Blender masks are sourced; (5) UI/art polish or further balance passes, user's call.</t>
         </is>
       </c>
     </row>
@@ -36622,7 +36622,7 @@
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>A yes/no design decision; Wave 4 item 27 if the carrier is Vaidya/Purohita</t>
+          <t>Design decision resolved 2026-09-15 (below); Wave 4 item 27 Monastery already exists as the carrier building</t>
         </is>
       </c>
       <c r="F39" s="56" t="inlineStr">
@@ -36632,7 +36632,7 @@
       </c>
       <c r="G39" s="22" t="inlineStr">
         <is>
-          <t>AoE II relics pay 0.5 gold/sec and can trigger a victory countdown - needs a carrier unit and a building to store them in.</t>
+          <t>DESIGN DECISION RESOLVED 2026-09-15 via AskUserQuestion: build it, economic only. Relics spawn on the map (or drop from destroyed scripted targets), carried by any land unit to a Monastery for a passive Gold trickle (AoE II precedent: 0.5-1x gold/sec per relic garrisoned). Explicitly NO new victory condition tied to relic count/ownership - stays purely economic, keeping scope smaller (user chose "Economic only" over "also add a Relic-count victory option" via AskUserQuestion). Monastery (Wave 4 item 27) is the existing carrier building - no new building needed. Not yet implemented - this was a design-decision-only session, not implementation.</t>
         </is>
       </c>
       <c r="H39" s="22" t="inlineStr">
@@ -36712,7 +36712,7 @@
       </c>
       <c r="G41" s="22" t="inlineStr">
         <is>
-          <t>Time Limit and Regicide are BOTH closed (Regicide pulled forward into Wave 4 item 28's own session, 2026-09-07, opt-in via GameSettings.RegicideEnabled). Wonder and Relic victory conditions remain unbuilt - building all of AoE's victory conditions is not automatically the right scope for this project, flagged as a decision, not an oversight.</t>
+          <t>Time Limit and Regicide are BOTH closed (Regicide pulled forward into Wave 4 item 28's own session, 2026-09-07, opt-in via GameSettings.RegicideEnabled). Wonder and Relic victory conditions remain unbuilt - building all of AoE's victory conditions is not automatically the right scope for this project, flagged as a decision, not an oversight. Wonder is DECLINED as of 2026-09-15 (AskUserQuestion: user did not pick the "Wonder + King-of-the-Hill-style victory" option) - no Wonder building, no Wonder-triggered victory countdown. Relic victory condition also declined (see item 35 - economic only, no new win condition). King of the Hill IS approved as a victory condition, but scoped under item 38 (Game modes) since the user picked it there specifically, not as a Wonder-KotH hybrid.</t>
         </is>
       </c>
       <c r="H41" s="22" t="inlineStr">
@@ -36742,7 +36742,7 @@
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>Item 37 if modes are tied to specific victory conditions</t>
+          <t>Design decision resolved 2026-09-15 (below)</t>
         </is>
       </c>
       <c r="F42" s="56" t="inlineStr">
@@ -36752,7 +36752,7 @@
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>Selectable Skirmish/Deathmatch/Regicide-style/Empire-Wars-style modes on top of the scenario system that already exists.</t>
+          <t>DESIGN DECISION RESOLVED 2026-09-15 via AskUserQuestion: build Deathmatch + King of the Hill this wave (not Empire Wars, not asked about). Deathmatch: opt-in GameSettings toggle (same pattern as RegicideEnabled) - match starts with large stockpiles of every resource and a higher starting Age, reusing existing resource-grant/age-set code paths, skips the early economy game. King of the Hill: a map-marked zone; the faction holding it uncontested for N minutes wins - needs a new zone-control tracker and countdown (shape similar to SurviveSeconds objectives but faction-vs-faction and area-based), a genuinely new victory condition (see item 37). Not yet implemented - this was a design-decision-only session; each of Deathmatch/KotH/Relic-Monastery is its own future one-item-per-session pickup per this project's own protocol.</t>
         </is>
       </c>
       <c r="H42" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30270,7 +30270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -30866,7 +30866,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>- UI: ornate HUD art pass (UI_ART_BRIEF Tiers 1-3), AoE-style single bottom bar, paginated icon command grid with tooltips, group-selection icon row, an always-visible Age/research meter, and (2026-09-14) SelectedUnitPanel portrait display wiring for the 21 generic-unit portraits, including TradeShipFactory's IconKey.</t>
+          <t>- UI: ornate HUD art pass (UI_ART_BRIEF Tiers 1-3), AoE-style single bottom bar, paginated icon command grid with tooltips, group-selection icon row, an always-visible Age/research meter, and (2026-09-14) SelectedUnitPanel portrait display wiring for the 21 generic-unit portraits, including TradeShipFactory's IconKey. (2026-09-16) Age-tiered TownCenter/Tower/Wall models (Ancient/Classical/Durg) decimated to the same ~500,000-tri ceiling as the 45 Imperial-tier models, except Wall_Durg (corrupted shared source, see Blocked table).</t>
         </is>
       </c>
     </row>
@@ -31038,98 +31038,117 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Fish Trap</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Art sourcing</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>The Farm half of the renewable-resource item closed 2026-09-03; the Fish Trap half was never started.</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Wall_Durg model (shared, all 5 civs)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Corrupted source FBX</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Reports 0 vertices/bounds while triangles.Length still claims ~3.08M stale indices - reproduced on a fresh-GUID copy, ruling out cache/import causes. Needs a re-exported source; currently spawns un-decimated via the existing fallback chain.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Store / marketing assets</t>
+          <t>Fish Trap</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>A user decision</t>
+          <t>Art sourcing</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Needs an explicit ruling on whether public release is a goal before it can even be scoped.</t>
+          <t>The Farm half of the renewable-resource item closed 2026-09-03; the Fish Trap half was never started.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>Store / marketing assets</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>A user decision</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Needs an explicit ruling on whether public release is a goal before it can even be scoped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>Relics + Monastery (35), Deathmatch (38), King of the Hill (37/38) - all scoped 2026-09-15, none implemented yet</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>A design decision</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Building all of AoE's victory conditions is not automatically the right scope for this project - flagged as a decision, not an oversight.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="63"/>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>KNOWN OPEN BUGS AND RISKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="22" t="inlineStr">
-        <is>
-          <t>- Two pre-existing BuildingModelFactoryTests failures (Chola TownCenter model) are the stable baseline in every recent session - 520 of 522 EditMode tests pass.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>- A second, concurrent session was observed committing to this same branch on 2026-09-14. Re-check git status before every commit.</t>
+          <t>- The 2 previously-standing BuildingModelFactoryTests failures (Chola TownCenter model) are gone as of 2026-09-16 - 581/581 EditMode tests pass, up from 520/522.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="22" t="inlineStr">
         <is>
+          <t>- A second, concurrent session was observed committing to this same branch on 2026-09-14. Re-check git status before every commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
           <t>- Recurring environment traps worth knowing: Unity's MCP console bridge can report zero errors while code genuinely fails to compile (check ~/Library/Logs/Unity/Editor.log directly), and exiting Play mode does not itself trigger a domain reload, so static state can bleed into the next EditMode run.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="22" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="22" t="n"/>
+    </row>
+    <row r="69"/>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>WHAT'S NEXT (pointer, not a commitment)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="22" t="inlineStr">
-        <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15, every decision-free Wave 6 item is closed (Town Bell, idle-worker indicator, cheat codes, Score system, Tutorial content), AND the Relics/Wonder/game-modes design decision is now resolved (Relics+Monastery economic-only, Deathmatch, King of the Hill; Wonder declined). What's left: (1) implement Relics + Monastery collection (35); (2) implement Deathmatch mode (38); (3) implement King of the Hill zone-control victory (37/38); (4) unit-side team colour once Blender masks are sourced; (5) UI/art polish or further balance passes, user's call.</t>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15, every decision-free Wave 6 item is closed (Town Bell, idle-worker indicator, cheat codes, Score system, Tutorial content), AND the Relics/Wonder/game-modes design decision is now resolved (Relics+Monastery economic-only, Deathmatch, King of the Hill; Wonder declined). Age-tiered building mesh decimation (the last flagged follow-up from the 2026-09-15 regression fix) closed 2026-09-16. What's left: (1) implement Relics + Monastery collection (35); (2) implement Deathmatch mode (38); (3) implement King of the Hill zone-control victory (37/38); (4) unit-side team colour once Blender masks are sourced; (5) UI/art polish or further balance passes, user's call.</t>
         </is>
       </c>
     </row>

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -234,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,6 +360,7 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -31105,7 +31106,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
@@ -31137,7 +31137,6 @@
     <row r="68">
       <c r="A68" s="22" t="n"/>
     </row>
-    <row r="69"/>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -32042,7 +32041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -32639,7 +32638,7 @@
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>a South Asian light-armored archer specialized against archers, quilted cotton armor, small round buckler shield strapped to the forearm, short recurve bow and quiver, neutral A-pose, front view. [STATUS: not sourced, reuses shared Archer body]</t>
+          <t>a bare, GEARLESS South Asian light-infantry body built for a fast skirmishing archer - lean/agile build, simple quilted cotton undergarment only (thin padded gambeson, no armor plates, no metal), bare head with no helmet, hands empty and relaxed with no shield or bow modeled onto the mesh. Helmet, forearm buckler, and bow are separate equippable game-asset props attached at runtime via bone sockets from the per-civ gear system (WeaponAttachment.cs), not baked into this body. Neutral A-pose, front and side view for a game character turnaround. [STATUS: not sourced - corrected 2026-09-16 to a gearless base body; reuses the shared Archer body rig, with helmet/shield/bow equipped separately per civ rather than baked into the model]</t>
         </is>
       </c>
     </row>
@@ -32813,10 +32812,18 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="59" t="inlineStr">
+        <is>
+          <t>RULE (corrected 2026-09-16): every new-unit HUMAN CHARACTER body (e.g. Skirmisher above, and the Maharaja hero below) must be sourced GEARLESS - no helmet, shield, or weapon baked onto the mesh. Helmet/shield/weapon are always separate equippable props attached at runtime via bone sockets (WeaponAttachment.AttachToBone), per the 'Per-civ unit gear' table above. Mount-only/machine-only/hull-only assets (Scout horse, Battering Ram, Scorpion, Fire Ship, etc.) are unaffected - they carry no character gear at all.</t>
+        </is>
+      </c>
+    </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="36" t="inlineStr">
         <is>
-          <t>Maharaja hero - one prompt per civilization (Wave 4 item 28, per-civ - shipped, all reuse shared body)</t>
+          <t>Maharaja hero (Wave 4 item 28) - ONE shared GEARLESS hero base body (prompt below) + a per-civ 'Royal/Hero tier' gear set (crown, ceremonial shield, ceremonial sword) in the table below, corrected 2026-09-16. The previous version baked each civ's ornate regalia directly onto 5 separate full-body models, which conflicts with the per-civ gear attachment system (item 5) this project actually uses - fixed to match that system instead.
+Shared hero base body prompt: "a bare, GEARLESS South Asian hero figure on foot, taller and more heroic build than the standard soldier body, simple unadorned royal undergarment/robe base layer only (no armor plates, no crown/helmet, no weapon or shield modeled onto the mesh) - crown, ceremonial armor accents, and ceremonial weapon/shield are separate equippable props attached at runtime via bone sockets, per civ, from the Royal/Hero gear table below. Regal neutral A-pose, front view." [Reused as one shared rig across all 5 civs; only the equipped Royal-tier gear differs per civ, exactly like the standard soldier per-civ gear table above.]</t>
         </is>
       </c>
       <c r="B46" s="37" t="n"/>
@@ -32832,12 +32839,24 @@
       </c>
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="C47" s="38" t="inlineStr"/>
-      <c r="D47" s="38" t="inlineStr"/>
-      <c r="E47" s="38" t="inlineStr"/>
+          <t>Royal Helmet / Crown</t>
+        </is>
+      </c>
+      <c r="C47" s="38" t="inlineStr">
+        <is>
+          <t>Ceremonial Shield</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>Ceremonial Weapon</t>
+        </is>
+      </c>
+      <c r="E47" s="38" t="inlineStr">
+        <is>
+          <t>Full prompt</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="75" customHeight="1">
       <c r="A48" s="39" t="inlineStr">
@@ -32847,7 +32866,22 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>a South Asian Chola Maharaja hero on foot, richly ornate ceremonial armor with bronze relief work and temple-gopuram motifs, royal crown/ceremonial helmet with Nandi-bull or lotus finial, ceremonial sword with bronze basket-hilt, rich royal robes, regal neutral A-pose, front view - the single most elaborate figure of this civilization.</t>
+          <t>Ornate bronze crown, Nandi-bull or lotus finial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ceremonial shield, temple-gopuram motif bronze relief rim</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ceremonial curved sword (patta-style), bronze basket-hilt, rope-motif engraving</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>a separate equippable Royal-tier gear set for the Chola Maharaja - ornate bronze crown with Nandi-bull/lotus finial, ceremonial shield with temple-gopuram motif bronze relief rim, ceremonial patta-style sword with bronze basket-hilt and rope-motif engraving, three separate equippable game-asset props on a plain background, front and side view each - grander than the civ's Imperial-tier soldier gear but the same attachment convention.</t>
         </is>
       </c>
     </row>
@@ -32859,7 +32893,22 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>richly ornate ceremonial armor with gold and granite-toned accents, elephant-and-lotus relief motifs, royal crown with elephant-tusk crest motif, ceremonial sword with mandapa-pillar-fluted hilt, rich royal robes, regal neutral A-pose, front view.</t>
+          <t>Crown with full elephant-tusk crest motif, gold accents</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ceremonial shield, full elephant-and-lotus relief medallion, gold/granite tones</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ceremonial sword with mandapa-pillar-fluted gilt hilt</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>a separate equippable Royal-tier gear set for the Vijayanagara Maharaja - crown with full elephant-tusk crest and gold accents, ceremonial shield with elephant-and-lotus relief medallion in gold/granite tones, ceremonial sword with mandapa-pillar-fluted gilt hilt, three separate equippable game-asset props on a plain background, front and side view each - grander than the civ's Imperial-tier soldier gear but the same attachment convention.</t>
         </is>
       </c>
     </row>
@@ -32871,7 +32920,22 @@
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>richly ornate ceremonial armor in rose-pink and gilt tones with jharokha-lattice engraving, royal crown/turban with full chhatri-dome crest and plume, ceremonial talwar/katar with gilt hilt and floral chasing, rich royal robes, regal neutral A-pose, front view.</t>
+          <t>Ornate crown/turban, full chhatri-dome crest and plume, gilt trim</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ceremonial shield, painted jharokha-lattice medallion, rose-pink and gilt accents</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ceremonial talwar or katar, gilt hilt, floral chasing</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>a separate equippable Royal-tier gear set for the Rajput Maharaja - ornate crown/turban with full chhatri-dome crest, plume, and gilt trim, ceremonial shield with painted jharokha-lattice medallion in rose-pink and gilt, ceremonial talwar/katar with gilt hilt and floral chasing, three separate equippable game-asset props on a plain background, front and side view each - grander than the civ's Imperial-tier soldier gear but the same attachment convention.</t>
         </is>
       </c>
     </row>
@@ -32883,7 +32947,22 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>richly ornate mirror-polished ceremonial armor, royal crown crested with full four-lion Ashokan capital, ceremonial sword with lion-headed pommel, rich royal robes, regal neutral A-pose, front view.</t>
+          <t>Mirror-polished crown, full four-lion Ashokan capital crest</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ceremonial shield, stupa-dome medallion and lion motif, mirror-polished trim</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ceremonial sword with lion-headed pommel</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>a separate equippable Royal-tier gear set for the Maurya Maharaja - mirror-polished crown with full four-lion Ashokan capital crest, ceremonial shield with stupa-dome medallion and lion motif in mirror-polished trim, ceremonial sword with lion-headed pommel, three separate equippable game-asset props on a plain background, front and side view each - grander than the civ's Imperial-tier soldier gear but the same attachment convention.</t>
         </is>
       </c>
     </row>
@@ -32895,14 +32974,29 @@
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>ceremonial armor deliberately more restrained than other civs' heroes per Maratha's hill-fort identity - dark iron and leather with saffron-and-black royal accents rather than heavy gilding, modest crowned helmet with saffron plume, ceremonial firangi-style sword with saffron-and-black hilt wrap, regal but understated, front view.</t>
+          <t>Dark-iron crowned helmet, saffron-accented plume</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ceremonial shield, hill-fort bastion motif, saffron-and-black trim</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ceremonial curved sword (firangi-style), saffron-and-black hilt wrap</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>a separate equippable Royal-tier gear set for the Maratha Maharaja - deliberately understated per the civ's hill-fort identity: dark-iron crowned helmet with saffron-accented plume, ceremonial shield with hill-fort bastion motif and saffron-and-black trim, ceremonial firangi-style sword with saffron-and-black hilt wrap, three separate equippable game-asset props on a plain background, front and side view each - still more ornate than the civ's own Imperial-tier soldier gear, but restrained compared to every other civ's Royal tier.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>STATUS: implemented (Wave 4 item 28, 2026-09-07) - but no dedicated per-civ Maharaja model was ever sourced from these prompts; every civ's Maharaja reuses the shared Human Character Dummy + Horse + Sword combo (same as Rajput Royal Guard), visually identical to a Cavalry/Royal-Guard hybrid.</t>
+          <t>STATUS: implemented (Wave 4 item 28, 2026-09-07) using the shared Human Character Dummy + Horse + Sword combo (no dedicated hero model sourced) - visually identical to a Cavalry/Royal-Guard hybrid today. The prompts above were corrected 2026-09-16 (gearless shared hero body + per-civ Royal-tier gear, replacing 5 fully-baked ornate bodies) for whenever a dedicated Maharaja model is actually sourced.</t>
         </is>
       </c>
     </row>
@@ -33024,7 +33118,7 @@
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="39" t="inlineStr">
         <is>
-          <t>New-unit human characters (Skirmisher, Vaidya, Purohita)</t>
+          <t>New-unit human characters (Skirmisher, Vaidya, Purohita) - GEARLESS bodies; helmet/shield/weapon props use the per-civ gear poly target above</t>
         </is>
       </c>
       <c r="B63" s="22" t="inlineStr">
@@ -33109,7 +33203,7 @@
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>Maharaja hero (per civ, solo figure)</t>
+          <t>Maharaja hero base body (shared, GEARLESS, per civ Royal-tier gear equipped separately - see per-civ gear poly target above for those props)</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
@@ -33119,7 +33213,7 @@
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>6,000-10,000 tris</t>
+          <t>2,500-4,500 tris (bare body only, taller/heroic build vs. standard soldier); Royal-tier gear props 200-600 tris each</t>
         </is>
       </c>
     </row>
@@ -33140,40 +33234,327 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="36" t="inlineStr">
+        <is>
+          <t>Wall System Session B: Corner &amp; End-Cap pieces (auto-tiling art, added 2026-09-16)</t>
+        </is>
+      </c>
+      <c r="B71" s="36" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>Ready-to-paste Gemini prompts for the corner/end-cap pieces Session B (drag-placement wall auto-tiling - see CLAUDE.md's matching status entry and the Roadmap - Open Items sheet) needs before it can be built. Matches the exact style-anchor convention at the top of this sheet and the isolated-object/three-quarter-isometric/plain-background convention already used for every other building concept image in this project. Once generated, convert each through Meshy AI same as every other sourced building asset, then hand the FBX/albedo/normal/metallicSmoothness files back for wiring via BuildingMeshDecimator.cs/MeshyBuildingImporter.cs. NOTE (2026-09-16, user-supplied reference images confirmed the corner design): the corner piece's own pillar/post region can likely be extracted (via triangle-cluster mesh-splitting, no Blender needed) and reused directly as the End-Cap piece, matching AoE's real Pillar+Plank asset convention - the End-Cap prompts below may turn out unnecessary once the real corner mesh is in hand and checked; hold off generating them until that's confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="38" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B74" s="38" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="C74" s="38" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Ancient (shared, wooden palisade)</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>Fortification wall corner concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background. Matches an existing straight wall segment made of sharpened wooden stakes lashed together with rope and leather bindings at intervals, uneven stake heights with pointed tops, sitting on a low rough stone-and-rubble foundation course. The corner piece shows two wall faces meeting at a right angle, with the same stake density and lashing detail continuing around the turn - not two straight segments crudely overlapped. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="90" customHeight="1">
+      <c r="A76" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B76" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Classical (shared, fieldstone)</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>Fortification wall corner concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background. Matches an existing straight wall segment built from irregular stacked fieldstone blocks in uneven weathered grey-brown coursing, with a slightly raised rough parapet lip along the top edge. The corner piece shows two wall faces meeting at a right angle with a genuine interlocking quoin-style stone bond at the turn (alternating overlap, like real masonry corners), not two flat segments butted together. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="90" customHeight="1">
+      <c r="A77" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Durg (shared, stone rampart)</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>Fortification wall corner concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background. Matches an existing straight wall segment built from neat courses of cut dressed stone blocks, with a slightly battered (inward-sloping) base, pillared bastion-style pilasters at intervals, narrow arrow-slit apertures along the upper band, and rectangular crenellations/merlons along the top edge. The corner piece shows a reinforced pillared bastion turret exactly at the 90-degree turn where the two wall faces meet, matching the pilaster style already on the straight segment. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="90" customHeight="1">
+      <c r="A78" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Chola (Imperial)</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>Chola civilization Wall Corner building concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Dravidian temple architecture - granite and sandstone construction, stepped pyramidal gopuram-tower motifs, tiered stone terraces, and intricate carved relief work. The corner piece shows two fortification wall faces meeting at a right angle with matching carved stonework and tiered detailing continuing around the turn. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="90" customHeight="1">
+      <c r="A79" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B79" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Vijayanagara (Imperial)</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>Vijayanagara civilization Wall Corner building concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Hampi-style Deccan architecture - monolithic weathered grey-brown granite blockwork, elephant and lotus relief carvings, and a flat corbelled roofline. The corner piece shows two fortification wall faces meeting at a right angle with matching granite blockwork and relief carving continuing around the turn. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="90" customHeight="1">
+      <c r="A80" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B80" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Rajput (Imperial)</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>Rajput civilization Wall Corner building concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by fort-and-haveli architecture - rose-pink sandstone walls, a domed chhatri pavilion at the corner, ornately latticed jharokha detailing, and a crenellated rampart parapet. The corner piece shows two fortification wall faces meeting at a right angle beneath the corner chhatri dome. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="90" customHeight="1">
+      <c r="A81" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Maurya (Imperial)</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>Mauryan imperial Wall Corner building concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Mauryan imperial architecture - polished cream Chunar sandstone with the famous Mauryan mirror-shine finish, lion-capital pillar motifs, and restrained massive geometric forms. The corner piece shows two fortification wall faces meeting at a right angle with matching polished sandstone and pillar detailing continuing around the turn. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="90" customHeight="1">
+      <c r="A82" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B82" s="39" t="inlineStr">
+        <is>
+          <t>Wall Corner - Maratha (Imperial)</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>Maratha civilization Wall Corner building concept art for a historical real-time strategy video game. A single isolated 90-degree wall corner/turn piece in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Deccan hill-fort architecture - rugged dark basalt stone construction, battered sloped bastion walls, a squat corner watch-burj, and minimal ornamentation, built for function over display. The corner piece shows a squat watch-burj bastion exactly at the 90-degree turn where the two wall faces meet. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="90" customHeight="1">
+      <c r="A83" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Ancient (shared, wooden palisade)</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>Fortification wall end-cap concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background. Matches an existing straight wall segment made of sharpened wooden stakes lashed together with rope and leather bindings, sitting on a low rough stone-and-rubble foundation. The terminal end is capped by a single stouter squared timber post, slightly taller than the surrounding stakes and with visible rope lashing wrapped around its top, so the wall clearly reads as deliberately ending rather than being cut off mid-structure. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="90" customHeight="1">
+      <c r="A84" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B84" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Classical (shared, fieldstone)</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>Fortification wall end-cap concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background. Matches an existing straight wall segment built from irregular stacked fieldstone blocks in uneven weathered grey-brown coursing. The terminal end is capped by a solid squared stone pier slightly thicker than the wall itself, with a small flat stone cap on top, so it reads as a finished stub rather than broken masonry. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="90" customHeight="1">
+      <c r="A85" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B85" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Durg (shared, stone rampart)</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>Fortification wall end-cap concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background. Matches an existing straight wall segment built from neat courses of cut dressed stone with pillared bastion-style pilasters and rectangular crenellations. The terminal end is capped by one of the wall's own pillared bastion pilasters, matching the corner piece's pilaster style, with a single merlon centered on the flat terminal face. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="90" customHeight="1">
+      <c r="A86" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B86" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Chola (Imperial)</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Chola civilization Wall End-Cap building concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a fortification wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Dravidian temple architecture. The terminal end is capped by a small stepped gopuram-finial post matching the wall's own granite and sandstone carved-relief style. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="90" customHeight="1">
+      <c r="A87" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B87" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Vijayanagara (Imperial)</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>Vijayanagara civilization Wall End-Cap building concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a fortification wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Hampi-style Deccan architecture. The terminal end is capped by a monolithic granite pillar stub with a carved lotus finial, matching the wall's own weathered grey-brown blockwork. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="90" customHeight="1">
+      <c r="A88" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B88" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Rajput (Imperial)</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>Rajput civilization Wall End-Cap building concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a fortification wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by fort-and-haveli architecture. The terminal end is capped by a small chhatri-domed post in rose-pink sandstone, matching the wall's own jharokha-latticed style. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="90" customHeight="1">
+      <c r="A89" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B89" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Maurya (Imperial)</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>Mauryan imperial Wall End-Cap building concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a fortification wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Mauryan imperial architecture. The terminal end is capped by a polished cream Chunar sandstone pillar stub with a small lion-capital cap, matching the wall's own mirror-shine finish. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="90" customHeight="1">
+      <c r="A90" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B90" s="39" t="inlineStr">
+        <is>
+          <t>Wall End-Cap - Maratha (Imperial)</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Maratha civilization Wall End-Cap building concept art for a historical real-time strategy video game. A single isolated wall end-cap piece - where a fortification wall line terminates cleanly - in a three-quarter isometric view, centered and fully visible on a plain neutral light background, inspired by Deccan hill-fort architecture. The terminal end is capped by a squat dark-basalt watch-post, deliberately unornamented, matching the wall's own rugged battered-stone style. No other buildings, characters, ground clutter, or scenery in the shot. [STATUS: NOT STARTED - Session B (wall auto-tiling), needs Gemini generation + Meshy AI conversion, then wire via BuildingMeshDecimator/MeshyBuildingImporter same as every other building asset]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="44">
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C41:E41"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C84:E84"/>
     <mergeCell ref="C40:E40"/>
-    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="C90:E90"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="C43:E43"/>
     <mergeCell ref="C60:E60"/>
     <mergeCell ref="C65:E65"/>
     <mergeCell ref="C36:E36"/>
-    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="C76:E76"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="C61:E61"/>
     <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C82:E82"/>
     <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C81:E81"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C66:E66"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C37:E37"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B48:E48"/>
     <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C86:E86"/>
     <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C77:E77"/>
     <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C83:E83"/>
     <mergeCell ref="C62:E62"/>
     <mergeCell ref="C42:E42"/>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C88:E88"/>
     <mergeCell ref="C64:E64"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C85:E85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33185,7 +33566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34595,6 +34976,41 @@
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="120" customHeight="1">
+      <c r="A49" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>AoE IV-style click-drag wall system (4-session epic)</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>User-requested feature</t>
+        </is>
+      </c>
+      <c r="D49" s="53" t="inlineStr">
+        <is>
+          <t>[~] Partial</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>Session A (free-angle drag-placement of the existing Wall segment) closed 2026-09-16 - see CLAUDE.md's matching status entry. Session B (auto-tiling corner/end-cap pieces, min-3-segment build rule) is blocked on art: corner/end-cap Gemini-&gt;Meshy prompts for all 3 shared pre-Imperial tiers (Ancient/Classical/Durg) plus all 5 civs' Imperial tier are in the 'Art Generation Prompts' sheet (Wall System Session B section, added 2026-09-16). User-supplied corner reference renders confirmed the Classical/Durg style briefs are correct. Open question flagged in that sheet: the corner mesh's own pillar/post region may be extractable and reusable directly as the End-Cap piece (matching AoE's real Pillar+Plank convention) - confirm once the real Meshy geometry is in hand before generating the separate End-Cap images. Session C (gate-interlocking - a Gate placed over a wall line absorbs the overlapping segments and inserts junction pieces) and Session D (a vertex-shader/progress-driven construction-rise visual, replacing ConstructionSite's current scale-squash animation - fully independent of A/B/C, could be done anytime) remain unstarted.</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>CLAUDE.md / Art Generation Prompts sheet</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr">
         <is>
           <t>Roadmap - Open Items &amp; Priority</t>
         </is>

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -32262,12 +32262,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Simple leather/quilted skull-cap, no metal</t>
+          <t>None - no helmet equipped at this age (bare head)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>Plain wood-and-hide round shield, unpainted</t>
+          <t>None - no shield equipped at this age (empty off-hand)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>a basic soldier's equipment set for the earliest age, deliberately plain and generic - no civ ornamentation: simple leather/quilted skull-cap, plain wood-and-hide round shield with no markings, unadorned iron short sword or spearhead with plain wood haft, three separate equippable game-asset pieces on a plain background, front and side view each.</t>
+          <t>CORRECTED 2026-09-17 (progressive gear unlock, shared tiers only - Durg/Imperial civ-specific rows below are unaffected): at Ancient age a soldier is equipped with a WEAPON ONLY - bare head, empty off-hand, no helmet or shield exists yet at this tier. Source only one prop: an unadorned iron short sword or spearhead with a plain wood haft, on a plain background, front and side view. Do not generate an Ancient-tier helmet or shield - they are not equipped until Classical (helmet) and remain absent until civ-specific Durg gear introduces a shield (see row below - Classical keeps its own shield as already specified, this rule only removes Ancient's).</t>
         </is>
       </c>
     </row>
@@ -32621,7 +32621,7 @@
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>a lean, fast South Asian riding horse with simple saddle/bridle/lightweight saddle-cloth, no rider, standing neutral pose, all four legs visible, front view, orthographic. [STATUS: not sourced, reuses shared Cavalry horse]</t>
+          <t>a bare, GEARLESS lean/fast South Asian riding horse - plain coat, no saddle-cloth ornamentation or civ markings baked onto the mesh, bare tack only (a simple neutral bridle/girth strap modeled as part of the horse is fine since it carries no civ identity) - any saddle-cloth, barding, or civ-colored tack accent is a separate attachable prop (reins/chest/head socket points), not part of this body. No rider. Standing neutral pose, all four legs visible, front view, orthographic. [STATUS: not sourced, this is the ONE shared mount reused by Scout, Cavalry, Cavalry Archer, Rajput Royal Guard, and Maratha Mavla Raider - only the rider mesh/gear on top changes per unit]</t>
         </is>
       </c>
     </row>
@@ -32672,7 +32672,7 @@
       </c>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>a swift, lightly-armored South Asian riding horse suited for a mounted archer, no rider, neutral pose, front view, orthographic. [STATUS: not sourced, reuses shared Cavalry horse + Bow prop]</t>
+          <t>reuses the identical shared Cavalry horse mount from row above (Scout) - do not source a second horse model. The mounted-archer look comes entirely from the rider's own gearless body + a bow prop attached to the rider's hand socket, not from a different horse. [STATUS: not sourced as a separate asset - shares the Scout/Cavalry horse mount, differs only by rider + attached Bow prop]</t>
         </is>
       </c>
     </row>
@@ -32689,7 +32689,7 @@
       </c>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>a South Asian riding camel in desert/arid-region tack, simple saddle, no rider, neutral pose, front view, orthographic. [STATUS: not sourced, reuses shared Cavalry+Spearman props]</t>
+          <t>a bare, GEARLESS South Asian riding camel, plain coat and bare tack only (a simple neutral bridle/girth strap modeled as part of the camel is fine since it carries no civ identity) - no saddle-cloth ornamentation, blanket pattern, or civ-colored tack baked onto the mesh; any civ accent belongs on the rider's own per-civ gear, not the mount. No rider. Standing neutral pose, all four legs visible, front view, orthographic. [STATUS: not sourced - a second shared mount, distinct from the Cavalry horse, used only by Camel Rider]</t>
         </is>
       </c>
     </row>
@@ -32815,7 +32815,8 @@
     <row r="45">
       <c r="A45" s="59" t="inlineStr">
         <is>
-          <t>RULE (corrected 2026-09-16): every new-unit HUMAN CHARACTER body (e.g. Skirmisher above, and the Maharaja hero below) must be sourced GEARLESS - no helmet, shield, or weapon baked onto the mesh. Helmet/shield/weapon are always separate equippable props attached at runtime via bone sockets (WeaponAttachment.AttachToBone), per the 'Per-civ unit gear' table above. Mount-only/machine-only/hull-only assets (Scout horse, Battering Ram, Scorpion, Fire Ship, etc.) are unaffected - they carry no character gear at all.</t>
+          <t>RULE (corrected 2026-09-16): every new-unit HUMAN CHARACTER body (e.g. Skirmisher above, and the Maharaja hero below) must be sourced GEARLESS - no helmet, shield, or weapon baked onto the mesh. Helmet/shield/weapon are always separate equippable props attached at runtime via bone sockets (WeaponAttachment.AttachToBone), per the 'Per-civ unit gear' table above. Mount-only/machine-only/hull-only assets (Scout horse, Battering Ram, Scorpion, Fire Ship, etc.) are unaffected - they carry no character gear at all.
+The same rule extends to MOUNTS: no saddle-cloth/barding/civ ornamentation baked onto a horse or camel body - any civ-colored tack or barding is a separate attachable prop, exactly like rider gear. AUDIT FLAG (not yet verified either way): the existing Maurya/Vijayanagara War Elephant models predate this rule and were never checked for whether their howdah/mahout platform is a separate mesh from the elephant body - re-verify before assuming they already comply, and re-source with a bare-elephant-body prompt (elephant only, no howdah/armor baked on, mahout rider reusing the shared humanoid body, howdah as its own separate attachable structure) if they don't.</t>
         </is>
       </c>
     </row>

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30296,6 +30296,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -30306,7 +30307,7 @@
     <row r="5" ht="74" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave; 5 of its 9 items (Town Bell, idle-worker indicator, cheat codes, Score system, tutorial content) are done - every decision-free item is now closed. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Remaining Wave 6 items (Relics, Wonder/KotH victory conditions, game modes) all need a design decision first; otherwise development is a long tail of UI/art polish and asset sourcing.</t>
+          <t>Waves 0 through 5 of docs/IMPLEMENTATION_ROADMAP.md are ALL CLOSED (2026-09-04 to 2026-09-14). Wave 6 - the parallel-safe economy/meta backlog - is the only open wave; 6 of its 9 items (Town Bell, idle-worker indicator, cheat codes, Score system, tutorial content, Relics + Monastery collection) are done. The AoE-parity plan's Phases 1-4 are resolved and Phase 5 (multiplayer) is complete except for testing that needs a second physical machine. Remaining Wave 6 items (Relics, Wonder/KotH victory conditions, game modes) all need a design decision first; otherwise development is a long tail of UI/art polish and asset sourcing.</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -30315,6 +30316,7 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -30534,10 +30536,11 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>OPEN. Items 33 (Town Bell) and 34 (idle-worker indicator) closed 2026-09-14. Remaining: Relics + relic storage (35), Score system (36), Wonder/Relic victory conditions (37), game modes (38), cheat codes (39), tutorial content (40), soundtrack.</t>
-        </is>
-      </c>
-    </row>
+          <t>OPEN. Items 33, 34, 36, 39, 40 and 35 (Relics + Monastery collection, closed 2026-09-17) are done. Remaining: Wonder/Relic victory conditions (37, King of the Hill half still open), game modes (38, Deathmatch + King of the Hill), soundtrack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -30677,6 +30680,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -30808,6 +30812,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -30871,6 +30876,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
@@ -30895,6 +30901,7 @@
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="22" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -31106,6 +31113,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
@@ -31137,6 +31145,7 @@
     <row r="68">
       <c r="A68" s="22" t="n"/>
     </row>
+    <row r="69"/>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -31147,7 +31156,7 @@
     <row r="71">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. As of 2026-09-15, every decision-free Wave 6 item is closed (Town Bell, idle-worker indicator, cheat codes, Score system, Tutorial content), AND the Relics/Wonder/game-modes design decision is now resolved (Relics+Monastery economic-only, Deathmatch, King of the Hill; Wonder declined). Age-tiered building mesh decimation (the last flagged follow-up from the 2026-09-15 regression fix) closed 2026-09-16. What's left: (1) implement Relics + Monastery collection (35); (2) implement Deathmatch mode (38); (3) implement King of the Hill zone-control victory (37/38); (4) unit-side team colour once Blender masks are sourced; (5) UI/art polish or further balance passes, user's call.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. Relics + Monastery collection (35) closed 2026-09-17. What's left: (1) implement Deathmatch mode (38); (2) implement King of the Hill zone-control victory (37/38); (3) unit-side team colour once Blender masks are sourced; (4) UI/art polish or further balance passes, user's call.</t>
         </is>
       </c>
     </row>
@@ -37063,12 +37072,12 @@
       </c>
       <c r="F39" s="56" t="inlineStr">
         <is>
-          <t>[ ] Not Started</t>
+          <t>[OK] Implemented</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr">
         <is>
-          <t>DESIGN DECISION RESOLVED 2026-09-15 via AskUserQuestion: build it, economic only. Relics spawn on the map (or drop from destroyed scripted targets), carried by any land unit to a Monastery for a passive Gold trickle (AoE II precedent: 0.5-1x gold/sec per relic garrisoned). Explicitly NO new victory condition tied to relic count/ownership - stays purely economic, keeping scope smaller (user chose "Economic only" over "also add a Relic-count victory option" via AskUserQuestion). Monastery (Wave 4 item 27) is the existing carrier building - no new building needed. Not yet implemented - this was a design-decision-only session, not implementation.</t>
+          <t>Closed 2026-09-17. Implemented per the 2026-09-15 design decision: economic only, no new victory condition. New Resources/Relic.cs (neutral world prop, held/unheld flag) and Resources/RelicCarrier.cs (added to every land unit factory that already carries GarrisonSeeker - 20 factories - mirroring that item's own broad-add convention): right-click an unclaimed Relic picks it up (reparented onto the carrying unit, no dedicated carried-Relic art exists yet - flagged per the flag-asset-needs convention), auto-routes to the nearest owned Monastery (FindNearestOwnedMonastery, same shape as Trader.FindNearestOwnedMarket), and deposits automatically on arrival - a one-shot pickup-then-deliver, not an endless shuttle like Trader. A carrier that dies mid-carry drops the Relic at its death position (RelicCarrier.OnDestroy unparents it, live-verified). Monastery.cs gained RelicCount/AddRelic()/a passive Gold trickle (0.5 Gold/sec/Relic while complete, first-pass rate, not independently balanced, same disclosed convention as Trader's own ComputeTradeGold) via a new internal Tick(deltaTime) (Farm.Tick's own testability convention) and a pure RelicGoldPerTick formula. Relics spawn on the map via ResourceNodeSpawner.SpawnRelic (reuses its existing RNG/ring-placement convention; new MapDefinitionData.RelicCount=5 on every map, deliberately NOT scaled with map area like resource counts - Relics stay scarce regardless of map size). SelectionManager gained a hitRelic branch (neutral, no friendly-gate - any faction's unit can grab it first, matching AoE's own rule) plus CancelCarry() wired into every other order branch's cancel chain. 10 new EditMode tests (RelicTests.cs: held-state flag, FindNearestOwnedMonastery routing, RelicGoldPerTick formula, Monastery.Tick gold-trickle behavior - 601/601 total, up from 591, all pass). Live-verified via UnityMCP through the real production path: a real match (5 real Relics spawned on RiverValley, matching RelicCount), a real Monastery placed and completed, a real Player Worker's RelicCarrier.PickUp() reparented the Relic onto it (IsHeld=true, parent=Worker); left to run through its own real Update()/NavMeshAgent loop with no further intervention, the worker auto-walked ~38 units to the Monastery and deposited on its own (Monastery.RelicCount 0-&gt;1, Relic GameObject destroyed, 4 Relics remained in the scene); the real Player Gold stockpile was independently confirmed climbing on its own between two unrelated tool calls (17.6 -&gt; 21.0 -&gt; 24.2 over consecutive real wall-clock gaps, consistent with 0.5 Gold/sec for 1 held Relic and no other active Gold source in that match) - the live gold-trickle Update() loop, not just the isolated unit test. Separately live-verified the death-drop case: picked up a second Relic, destroyed the carrying Worker mid-route, and confirmed the Relic correctly reappeared unparented and IsHeld=false at the Worker's exact death position. Full EditMode suite re-confirmed 601/601 after exiting Play mode. No AI-side use of Relics (no AI pickup/delivery hook) - new capability, not existing behavior moved, matching every other Wave 4/6 item's own precedent for skipping the AI hook without calling it a regression.</t>
         </is>
       </c>
       <c r="H39" s="22" t="inlineStr">

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -30296,7 +30296,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -30316,7 +30315,6 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -30540,7 +30538,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -30680,7 +30677,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -30812,7 +30808,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -30876,7 +30871,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
@@ -30901,7 +30895,6 @@
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="22" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -31113,7 +31106,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
@@ -31145,7 +31137,6 @@
     <row r="68">
       <c r="A68" s="22" t="n"/>
     </row>
-    <row r="69"/>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -33576,7 +33567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35021,6 +35012,41 @@
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Wall mechanics audit vs. real AoE2 reference (2026-09-28)</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>User-requested feature (extends item 11)</t>
+        </is>
+      </c>
+      <c r="D50" s="53" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>User pasted AoE2's own wall-mechanics writeup and asked for an audit. Findings: (1) diagonal wall-gap blocking - NOT implemented (continuous NavMesh has no tile-diagonal concept; two Wall/Gate footprints diagonally adjacent with no orthogonal connector can leave a corner gap). (2) Foundation states ("quick-wall") - PARTIAL: a placed foundation's NavMeshObstacle carves (blocks movement) immediately on placement, not only after the first builder hit as AoE2 does; and ConstructionSite/Attackable has zero armor-deficit-while-incomplete mechanic (an unfinished foundation takes normal final armor, not a melee-damage-vulnerable state). (3) Auto-tiling (bitmask-driven piece selection) - NOT implemented as auto-tiling: piece choice is a manual Alpha1-5 hotkey (see WallFactory.WallPieceKind / BuildingPlacer.UpdateWallPieceSelection), not neighbor-derived - but since the Ancient and Classical/Durg tiers already have real art for all 5 piece kinds (Straight/Corner/EndPost/TJunction/XJunction, per the wall-kit sessions logged in CLAUDE.md), a neighbor-based auto-select is implementable NOW with zero new art, closing most of Session B's request without waiting on the still-blocked Imperial-tier corner/end-cap art. (4) Gate absorbing overlapping Wall segments (= Session C above) - NOT implemented; also code-only, no new art needed (delete+refund overlapping Wall(s), place Gate). (5) Fog-of-war wall-placement scanning - RE-CHECKED, already correctly implemented: BuildingFootprint.IsClear/BarracksFactory.IsClear both check Building.All (full ground truth, no per-faction vision filter), matching AoE2's own real behavior of blocking placement over an unseen enemy building/unit. No gap, no work needed. Plan: implement (1)/(2)/(3)/(4) as one planned multi-part session, in that order, each covered by EditMode tests and live UnityMCP verification before commit. CLOSED 2026-09-29: all 4 real gaps implemented and live-verified through the real production path (see CLAUDE.md's matching status entry and docs/SESSION_LOG.md for full detail) - foundation passable-until-first-hit + 0 melee armor while incomplete (ConstructionSite.cs/Attackable.cs, applies to all buildings), a geometric diagonal corner-seal (new WallCornerSeal.cs/WallCornerSealLink.cs), Gate absorbing overlapping same-faction Wall segments with a full refund (BuildingPlacer.cs), and fully automatic neighbor-based wall piece-kind selection replacing the removed Alpha1-5 hotkey scheme (new WallConnectivity.cs). 28 new EditMode tests, 897/897 pass (1 pre-existing, unrelated BuildingPrefabValidationTests NRE, same standing baseline).</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (wall-mechanics audit)</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
         <is>
           <t>Roadmap - Open Items &amp; Priority</t>
         </is>

--- a/docs/KingdomsOfBharat_Master_Reference.xlsx
+++ b/docs/KingdomsOfBharat_Master_Reference.xlsx
@@ -31147,7 +31147,7 @@
     <row r="71">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>The project's own session protocol is one roadmap item per session, user's call on which. Relics + Monastery collection (35) closed 2026-09-17. What's left: (1) implement Deathmatch mode (38); (2) implement King of the Hill zone-control victory (37/38); (3) unit-side team colour once Blender masks are sourced; (4) UI/art polish or further balance passes, user's call.</t>
+          <t>The project's own session protocol is one roadmap item per session, user's call on which. Relics + Monastery collection (35) closed 2026-09-17; the wall-mechanics-audit epic (item 12 on the Roadmap - Open Items &amp; Priority sheet) closed 2026-09-29. A full environment/terrain/map-design audit was also done 2026-09-29 and scoped into 6 new Open Backlog items (13-18 on that same sheet): wiring terrain-scale foliage (real tree/detail prototypes are never assigned, so PopulateTerrainFoliage silently no-ops every match - highest priority, recommended first - CLOSED 2026-09-29, see the Roadmap sheet's item 13 and docs/SESSION_LOG.md), terrain texture palette expansion, environmental set-dressing, map count/variety expansion, per-map biome/atmosphere variation, and a terrain performance profiling pass (run after foliage wiring). Item 18 (terrain performance profiling) is the natural next item in that same batch, since foliage wiring adds real, currently-unmeasured cost. What's left otherwise: (1) implement Deathmatch mode (38); (2) implement King of the Hill zone-control victory (37/38); (3) unit-side team colour once Blender masks are sourced; (4) UI/art polish or further balance passes, user's call.</t>
         </is>
       </c>
     </row>
@@ -33567,7 +33567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35047,6 +35047,216 @@
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>Wire terrain-scale foliage (forest tree/detail prototypes never assigned)</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker, sourcing only</t>
+        </is>
+      </c>
+      <c r="D51" s="53" t="inlineStr">
+        <is>
+          <t>[OK] Implemented</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-29 (environment/terrain audit). ResourceNodeSpawner.PopulateTerrainFoliage() and all Forest/Clearing classification logic already exist and are unit-tested, but nothing anywhere in the codebase ever assigns treePrototypes/detailPrototypes on the runtime-generated terrain (confirmed via direct grep - only ever read, never written), so the method silently no-ops every match and the game falls back to individual SpawnTree model placement. Practical effect: forests read as sparse scattered trees, not a painted canopy, and the Clearing map's entire design identity (dense forest + cut lanes) is currently invisible in play despite passing tests. Fix: source/generate real Nature Renderer 6-compatible tree/grass-detail prototypes, assign them on ProceduralTerrain's generated TerrainData at match start, verify PopulateTerrainFoliage actually returns true and paints. Size M. Risk: Nature Renderer's prototype format/GPU instancing has only been used in its own Editor demo scenes so far, not verified at runtime in this project - may need a native-Terrain-tree fallback if incompatible. Recommended first of this batch - unblocks item 18 (profiling) and benefits item 15 (set-dressing). CLOSED 2026-09-29: ProceduralTerrain.ApplyTreePrototypes now wires real tree prefabs (Resources/Environment/Trees/URP_Tree_1/2/3, already owned - no new sourcing needed) onto TerrainData.treePrototypes every Rebuild(); canopy placement now picks randomly among all resolved prototypes instead of a single fixed index. Used Unity's own native Terrain tree renderer, not Nature Renderer 6 - that package's Layer/Spawner setup is authored per fixed scene Terrain instance in its Editor window, which doesn't fit this project's terrain being rebuilt at runtime per match/map. Found during implementation that the detail(grass) half of this item was already solved elsewhere (TerrainClutter.cs's own GPU-instanced clutter renderer already paints real grass), so detailPrototypes stays deliberately unwired - scope narrowed to trees only. 896/897 EditMode tests pass unchanged (1 pre-existing, unrelated BuildingPrefabValidationTests NRE, standing baseline). Live-verified via UnityMCP through the real production path on 2 maps: SkirmishClearing (the map whose own design identity depended on this) painted 45,720 real trees with 4,215 gatherable ForestNode proxies, a full harvest-to-depletion of one proxy removed exactly 3 real trees from the terrain's own treeInstances array, and a real gameplay-camera screenshot confirms a dense, correctly-cut-laned forest canopy around the cleared starting plateau; RiverValley re-confirmed the fix generalizes. See docs/SESSION_LOG.md's matching entry for full detail.</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>Environment/terrain audit (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>Terrain texture palette expansion (only 5 layers, reused identically across all 7 maps)</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Art sourcing (2-3 additional textures)</t>
+        </is>
+      </c>
+      <c r="D52" s="53" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-29. Only 5 terrain layers exist project-wide (Grass/Dirt/Rock/Sand/wet-sand-pebbles), shared identically by every map style regardless of biome identity - Mountain Pass and Crossroad Valleys currently use the same rock/grass textures despite being visually distinct in geometry only. Scope: source 2-3 additional layers (e.g. arid/dry ground, darker forest floor) and/or per-style tinting of the existing 5 layers so each of the 7 maps reads as texturally distinct, wired into ProceduralTerrain.ApplyAlphamaps. Size M.</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>Environment/terrain audit (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Environmental set-dressing / non-gameplay decoration</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>Art sourcing (decorative models)</t>
+        </is>
+      </c>
+      <c r="D53" s="53" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-29. Nothing exists beyond functional clutter (grass/rocks/pebbles/reeds) and resource nodes - no ruins, shrines, decorative rock formations, dead trees, or any hand-authored visual interest; every map currently reads as procedurally generated because it is, uniformly. Scope: a new lightweight prop-scatter pass reusing ResourceBias.cs's mask-biased placement idiom for purely decorative, non-collidable objects, seeded per map style (temple ruins near Crossroad Valleys' mesas, cairns on Mountain Pass's ridge, etc.). Size M-L. Benefits from item 13 (foliage) landing first, since forest density affects where decoration reads well.</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>Environment/terrain audit (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>Map count / variety expansion (small/large size variants; new styles)</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Nothing for size variants; new-style design work for new archetypes</t>
+        </is>
+      </c>
+      <c r="D54" s="53" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-29. 7 maps total (5 styles + small/large variants of Crossroad Valleys only) - the other 4 styles (Divided Riverbed, Mountain Pass, Highland Foothills, Clearing) are medium-only. Two independent options: (a) extend small/large baking to the other 4 styles - mechanical, SkirmishMapScaling.cs already generalizes to any size, Size S; (b) author genuinely new style archetypes beyond the current 5 - bigger, needs new per-style carving logic mirroring the original 5-style session, Size L. Split into two separate future sessions if both are wanted; do not bundle.</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>Environment/terrain audit (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>Biome/atmosphere/weather variation per map</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker</t>
+        </is>
+      </c>
+      <c r="D55" s="53" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-29. Every map uses the identical global lighting/sky/fog/post-process Volume (Assets/Settings/MapPostProcess.asset) - no per-map or per-style atmospheric identity (no dusk lighting for a different mood, no haze variation between a river map and a mountain map). Scope: per-map (or per-style) lighting/Volume presets, swapped by MapId - the Volume framework already supports this, mostly authoring presets + a selection switch, no new system. Size S.</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>Environment/terrain audit (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap - Open Items &amp; Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B56" s="39" t="inlineStr">
+        <is>
+          <t>Terrain performance profiling at real scale (foliage + clutter cost unmeasured)</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>Nothing - zero blocker; should run after item 13</t>
+        </is>
+      </c>
+      <c r="D56" s="53" t="inlineStr">
+        <is>
+          <t>[ ] Not Started</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Scoped 2026-09-29. No profiling pass exists for terrain+clutter+foliage cost at large map size / populated match, and item 13 (wiring real foliage) would add new, currently-unmeasured cost on top. Scope: run mcp__UnityMCP__manage_profiler against a real large-map, populated match; check clutter renderer draw calls, terrain LOD behavior, and foliage cost once item 13 lands. Size S - tooling already exists. Should run immediately after item 13, since foliage is the single biggest unmeasured cost and gets more expensive to skip the longer it runs unprofiled.</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>Environment/terrain audit (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
         <is>
           <t>Roadmap - Open Items &amp; Priority</t>
         </is>
